--- a/Meses pasados.xlsx
+++ b/Meses pasados.xlsx
@@ -1,30 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emili\OneDrive\Escritorio\Visual\bitacora\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03F0FDE-6EFD-4118-8475-7DB98D152E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5688"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="387">
   <si>
     <t>DIA</t>
   </si>
@@ -675,13 +687,523 @@
   </si>
   <si>
     <t>Pizza y bananos</t>
+  </si>
+  <si>
+    <t>Enchiladas que hice con mamá</t>
+  </si>
+  <si>
+    <t>Frijoles con salsa sobrante</t>
+  </si>
+  <si>
+    <t>Pollo hecho en la freidora por papá</t>
+  </si>
+  <si>
+    <t>Licuado de sandia y banano</t>
+  </si>
+  <si>
+    <t>Hice tortillas con salsa</t>
+  </si>
+  <si>
+    <t>papá hizo webo en torta, frijokes y arroz</t>
+  </si>
+  <si>
+    <t>Lo que sobraba de tortillas ensalsadas</t>
+  </si>
+  <si>
+    <t>Licuado de sandia y minimo</t>
+  </si>
+  <si>
+    <t>Hice pollo a mi estilo, junto con arroz y frijoles</t>
+  </si>
+  <si>
+    <t>Un poco de pollo que sobró arroz</t>
+  </si>
+  <si>
+    <t>Papá hizo arroz, frijoles y webo estrellado</t>
+  </si>
+  <si>
+    <t>Mamá hizo una "sopa" de verduras y arroz</t>
+  </si>
+  <si>
+    <t>Pan bimbo con cafe</t>
+  </si>
+  <si>
+    <t>Hice mas arroz y me lo comi con la sopa sobrante</t>
+  </si>
+  <si>
+    <t>2 charamuscas de leche</t>
+  </si>
+  <si>
+    <t>Fuimos a comer a Comayagua, especificamente chuleta</t>
+  </si>
+  <si>
+    <t>Webo y pan molde con queso</t>
+  </si>
+  <si>
+    <t>Unos tacos que dejaron por ahi (estaban feos)</t>
+  </si>
+  <si>
+    <t>Jugo de sandia</t>
+  </si>
+  <si>
+    <t>Josef me hizo la cena: frijoles webo</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Sardinas y arroz</t>
+  </si>
+  <si>
+    <t>Galletas de soda con salsa y jugo de sandia</t>
+  </si>
+  <si>
+    <t>Cafe con pan y una galleta de soda</t>
+  </si>
+  <si>
+    <t>Galleta con salsa</t>
+  </si>
+  <si>
+    <t>Pan con cafe</t>
+  </si>
+  <si>
+    <t>La pasta que sobró de ayer</t>
+  </si>
+  <si>
+    <t>Tambien galleta con salsa</t>
+  </si>
+  <si>
+    <t>Una carnita que me trajonjosef y frijoles</t>
+  </si>
+  <si>
+    <t>Cuando llegue a comayagua comimos una parridad con mis padres</t>
+  </si>
+  <si>
+    <t>Una ensalada de papas que venia con un pollo que llevé</t>
+  </si>
+  <si>
+    <t>Las sobras de la carne de ayer mas un pollo que llevé el mismo dia y arroz, frioles licuados que hice</t>
+  </si>
+  <si>
+    <t>Webo y frijoles</t>
+  </si>
+  <si>
+    <t>La hamburguesa en tu casa mas el café</t>
+  </si>
+  <si>
+    <t>Galleta con salsa ranchera mas nestum</t>
+  </si>
+  <si>
+    <t>Hice pollito y arroz</t>
+  </si>
+  <si>
+    <t>Lo mismo de la tarde y Nestum</t>
+  </si>
+  <si>
+    <t>Comi en la colonia con mis papas, especificamentea arroz chino con fajitas y ensalada de papas</t>
+  </si>
+  <si>
+    <t>Josef nos llevo a comer afuera por el dia del maestro, comimos tacos mexicanos</t>
+  </si>
+  <si>
+    <t>Nestum</t>
+  </si>
+  <si>
+    <t>Mamá me trajo unos hotdogs de no se donde</t>
+  </si>
+  <si>
+    <t>sin datos</t>
+  </si>
+  <si>
+    <t>Mis papas me dieron halon a cane asi que comimos afuera en matambritas (estan mejores las de bigos)</t>
+  </si>
+  <si>
+    <t>Mama le llevó pizza a Alex pero tambien comi de ahí</t>
+  </si>
+  <si>
+    <t>Fui al dentista y luego comimos las de bigos</t>
+  </si>
+  <si>
+    <t>Webo, frijoles</t>
+  </si>
+  <si>
+    <t>Mamá hizó arroz, frijoles, pollito de pollomaster y con tajaditas cona salsa</t>
+  </si>
+  <si>
+    <t>Solo el Nestum creo</t>
+  </si>
+  <si>
+    <t>comi un pollo que habia hecho y nadie se lo come</t>
+  </si>
+  <si>
+    <t>1 taco que dejaron ahi</t>
+  </si>
+  <si>
+    <t>Hice carne molida, frijoles con queso y me comi unos pedazitos de carne de por ahi</t>
+  </si>
+  <si>
+    <t>Tambien hice arroz en la tarde y la carne que sobro de la tarde</t>
+  </si>
+  <si>
+    <t>Carnita de ayer con arroz y sardinas</t>
+  </si>
+  <si>
+    <t>Galleta con salsa y Nestum</t>
+  </si>
+  <si>
+    <t>Me hice unos hot dogs caseros</t>
+  </si>
+  <si>
+    <t>Un pollo que dejaron en la refri y frijoles</t>
+  </si>
+  <si>
+    <t>Como no habia luz Josef me pidio unos chiaquiles</t>
+  </si>
+  <si>
+    <t>1 pedazo de pizza que sobró y una galleta</t>
+  </si>
+  <si>
+    <t>Webito y frijoles</t>
+  </si>
+  <si>
+    <t>Me hice unas tortillas con queso derretido y algo de fijoles</t>
+  </si>
+  <si>
+    <t>Mi hermano hizo un arroz con camarones que estuve esperando desde la mañana</t>
+  </si>
+  <si>
+    <t>Me hice unos sandwiches caseros</t>
+  </si>
+  <si>
+    <t>Le ayudé a mamá a jacer unas enchiladas</t>
+  </si>
+  <si>
+    <t>Un poco de carne que sobró y tambien me hice unos frijoles con arroz</t>
+  </si>
+  <si>
+    <t>Salimos a comer y yo pedí chuleta...</t>
+  </si>
+  <si>
+    <t>"Pan de pan"</t>
+  </si>
+  <si>
+    <t>Nestum y luego en la feria un chocolate con guaro</t>
+  </si>
+  <si>
+    <t>Mamá hizo frijoles webo estrellado y arroz</t>
+  </si>
+  <si>
+    <t>Hice baleadas</t>
+  </si>
+  <si>
+    <t>Fuimos a rancho sofia y yo comí un sandwich cubano</t>
+  </si>
+  <si>
+    <t>En la refri dejaron unas tajadas asi que las comí con salsa y queso</t>
+  </si>
+  <si>
+    <t>Le ayudé a mamá a hacer enchiladas</t>
+  </si>
+  <si>
+    <t>Hice frijoles e Irma hizó frijoles con webo y platano</t>
+  </si>
+  <si>
+    <t>Grabita</t>
+  </si>
+  <si>
+    <t>Mamá e Irma hicieron pollo ensalsado con ensalada y tajadas</t>
+  </si>
+  <si>
+    <t>Arroz y sardinas</t>
+  </si>
+  <si>
+    <t>Jugo</t>
+  </si>
+  <si>
+    <t>La dona y la hamburguesa que me diste</t>
+  </si>
+  <si>
+    <t>Sopa magi y galleta con salsa</t>
+  </si>
+  <si>
+    <t>Pollo y arroz que dejaron por ahi</t>
+  </si>
+  <si>
+    <t>Nada</t>
+  </si>
+  <si>
+    <t>Josef compró pupusas</t>
+  </si>
+  <si>
+    <t>Un pollo que dejaron y un arroz ya hecho, ademas me hice un webo</t>
+  </si>
+  <si>
+    <t>Pollo que me trajó mamá</t>
+  </si>
+  <si>
+    <t>Dona que trajo mamá</t>
+  </si>
+  <si>
+    <t>Super lleno</t>
+  </si>
+  <si>
+    <t>Baleada en la mañana</t>
+  </si>
+  <si>
+    <t>Té que vomite</t>
+  </si>
+  <si>
+    <t>Deficiente(me sentia lleno)</t>
+  </si>
+  <si>
+    <t>Frijoles con platano</t>
+  </si>
+  <si>
+    <t>Josef me compró una carnita de torofuego y juego</t>
+  </si>
+  <si>
+    <t>Webo y pan molde con queso derretido</t>
+  </si>
+  <si>
+    <t>Vinieron mis papas y trajeron pizza</t>
+  </si>
+  <si>
+    <t>2 pedazos de pizza y la pasta de ayer</t>
+  </si>
+  <si>
+    <t>Unas sobras que dejaron de varias comidas y tambien hice paas hervidas y frijoles</t>
+  </si>
+  <si>
+    <t>Sandwich casero</t>
+  </si>
+  <si>
+    <t>Pan de queso</t>
+  </si>
+  <si>
+    <t>Josef me compró una burrita</t>
+  </si>
+  <si>
+    <t>Webo con tortilla y quesillo</t>
+  </si>
+  <si>
+    <t>Nacatamal que trajo Josef</t>
+  </si>
+  <si>
+    <t>Pizza que compré</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>En la mañana 2 pedazos de pizza de ayer, en cane tambien pizza que compraron</t>
+  </si>
+  <si>
+    <t>Lasaña que me diste y frijoles con queso</t>
+  </si>
+  <si>
+    <t>1 pedazo de pollo y fresco</t>
+  </si>
+  <si>
+    <t>Té de jengibre</t>
+  </si>
+  <si>
+    <t>Un pollo</t>
+  </si>
+  <si>
+    <t>Baleadas desnutridas</t>
+  </si>
+  <si>
+    <t>Solo quesadillas</t>
+  </si>
+  <si>
+    <t>Un café y un postre cuando salí con Dulce</t>
+  </si>
+  <si>
+    <t>Frijoles con carne molida</t>
+  </si>
+  <si>
+    <t>Pollo y arroz con ensalada</t>
+  </si>
+  <si>
+    <t>Tacos que compraron</t>
+  </si>
+  <si>
+    <t>Ayude a mamá a hacer ensalada con yajadas y pollo</t>
+  </si>
+  <si>
+    <t>Quesadillas y café</t>
+  </si>
+  <si>
+    <t>Mi hermano compró unos tacos el dia anterior pero me los comí hasta hoy</t>
+  </si>
+  <si>
+    <t>Hice sandwiches caseros</t>
+  </si>
+  <si>
+    <t>Lo que me dió tu hermana en la casa</t>
+  </si>
+  <si>
+    <t>Irma me dió una torta de frijoles y etc</t>
+  </si>
+  <si>
+    <t>Frijoles y pollo</t>
+  </si>
+  <si>
+    <t>Hamburguesa en la cita</t>
+  </si>
+  <si>
+    <t>Tortillas con quesillo, webo y algo de pollo</t>
+  </si>
+  <si>
+    <t>Coditos</t>
+  </si>
+  <si>
+    <t>Webo</t>
+  </si>
+  <si>
+    <t>Frijoles, unas papas, arroz y pollo</t>
+  </si>
+  <si>
+    <t>Tamalitos</t>
+  </si>
+  <si>
+    <t>Espaguetty</t>
+  </si>
+  <si>
+    <t>Espaguetty de nuevo</t>
+  </si>
+  <si>
+    <t>Irma me compró una baleada</t>
+  </si>
+  <si>
+    <t>Me hice un webo con pan molde tostado</t>
+  </si>
+  <si>
+    <t>Una baleada que dejaron por ahi</t>
+  </si>
+  <si>
+    <t>Tamalitos creo</t>
+  </si>
+  <si>
+    <t>Churro con salsa</t>
+  </si>
+  <si>
+    <t>Un tamalito</t>
+  </si>
+  <si>
+    <t>Webo y pan tostado antes de que llegaras</t>
+  </si>
+  <si>
+    <t>Josef me compró unas pupusas que estaban super deliciosas</t>
+  </si>
+  <si>
+    <t>Me hice una carne en la freidora, frijoles y junto un arroz que habia cené</t>
+  </si>
+  <si>
+    <t>Josef me dejó un webo y platano en la mañana</t>
+  </si>
+  <si>
+    <t>Comi tremenda comida con unas tajadas que dejaron en la refri, un tamalito y me hice unos frijoles</t>
+  </si>
+  <si>
+    <t>Me hice unas tortas con webo, frijoles, platano, queso derretido y chile (Delicioso)</t>
+  </si>
+  <si>
+    <t>Josef me trajo baleadas desnutridas</t>
+  </si>
+  <si>
+    <t>Comi bien tarde, carne, arroz, papa a modo de puré y frijoles licuados sobrantes</t>
+  </si>
+  <si>
+    <t>Coditos que hice evidentemente</t>
+  </si>
+  <si>
+    <t>Almorcé donde abuela y me dió una chuleta con frijoles y luego un poco de arroz chino que no se comió</t>
+  </si>
+  <si>
+    <t>Pastel de chocolate qe¿ue me dió abuela</t>
+  </si>
+  <si>
+    <t>Comi tarde algo de arroz y sardinas con algo de pasta que sobró</t>
+  </si>
+  <si>
+    <t>Un poco de frijoles y con arroz y hot dogs</t>
+  </si>
+  <si>
+    <t>2 donas que me trajeron mi padres</t>
+  </si>
+  <si>
+    <t>Irma hizo panqueques en la mañana</t>
+  </si>
+  <si>
+    <t>Josef me compró unso tacos</t>
+  </si>
+  <si>
+    <t>Hice coditos</t>
+  </si>
+  <si>
+    <t>Coditos de la tarde</t>
+  </si>
+  <si>
+    <t>Pan e hice un pollito con arroz y comi bien tarde</t>
+  </si>
+  <si>
+    <t>Comi un poco de pollo de ayer y arroz</t>
+  </si>
+  <si>
+    <t>Una lata de sardinas con 4 tortillas y una carne que hice en la freidora</t>
+  </si>
+  <si>
+    <t>Tambien me comí un batido proteinico con avena, granola, leche</t>
+  </si>
+  <si>
+    <t>Comi re tarde en cane un pedazo de pollo, arroz y 1 pedazo de pizza que mamá me dejó</t>
+  </si>
+  <si>
+    <t>Frijoles con encurtido con fresco</t>
+  </si>
+  <si>
+    <t>DOMINGO</t>
+  </si>
+  <si>
+    <t>LUNES</t>
+  </si>
+  <si>
+    <t>MARTES</t>
+  </si>
+  <si>
+    <t>MIERCOLES</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
+  </si>
+  <si>
+    <t>VIERNES</t>
+  </si>
+  <si>
+    <t>SABADO</t>
+  </si>
+  <si>
+    <t>NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>OCTUBRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,8 +1232,21 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -750,6 +1285,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCDCDCF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF28AE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8D1679"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8159D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,7 +1350,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -833,6 +1386,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1115,8 +1707,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="46.88671875" customWidth="1"/>
@@ -1126,7 +1718,7 @@
     <col min="16" max="16" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1181,8 +1773,62 @@
       <c r="R1" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>45453</v>
       </c>
@@ -1237,8 +1883,62 @@
       <c r="R2" s="12" t="s">
         <v>146</v>
       </c>
+      <c r="S2" s="13">
+        <v>45901</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y2" s="16">
+        <v>45931</v>
+      </c>
+      <c r="Z2" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC2" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" s="16">
+        <v>45962</v>
+      </c>
+      <c r="AF2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG2" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="AH2" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ2" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" ht="69" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>45454</v>
       </c>
@@ -1293,8 +1993,62 @@
       <c r="R3" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S3" s="13">
+        <v>45902</v>
+      </c>
+      <c r="T3" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="U3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="W3" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y3" s="16">
+        <v>45932</v>
+      </c>
+      <c r="Z3" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="AC3" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="AD3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE3" s="16">
+        <v>45963</v>
+      </c>
+      <c r="AF3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG3" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="AH3" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="AI3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ3" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>45455</v>
       </c>
@@ -1349,8 +2103,62 @@
       <c r="R4" s="12" t="s">
         <v>152</v>
       </c>
+      <c r="S4" s="13">
+        <v>45903</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="U4" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="V4" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="W4" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="X4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y4" s="16">
+        <v>45933</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>284</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB4" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="AC4" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD4" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE4" s="16">
+        <v>45964</v>
+      </c>
+      <c r="AF4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG4" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="AH4" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="AI4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ4" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>45456</v>
       </c>
@@ -1405,8 +2213,62 @@
       <c r="R5" s="12" t="s">
         <v>156</v>
       </c>
+      <c r="S5" s="13">
+        <v>45904</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="U5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="W5" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="X5" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y5" s="16">
+        <v>45934</v>
+      </c>
+      <c r="Z5" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="AA5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="AC5" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="AD5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE5" s="16">
+        <v>45965</v>
+      </c>
+      <c r="AF5" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AG5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH5" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="AI5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ5" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" ht="69" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>45457</v>
       </c>
@@ -1461,8 +2323,62 @@
       <c r="R6" s="12" t="s">
         <v>19</v>
       </c>
+      <c r="S6" s="13">
+        <v>45905</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="U6" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="V6" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="W6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X6" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y6" s="16">
+        <v>45935</v>
+      </c>
+      <c r="Z6" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC6" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="AD6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE6" s="16">
+        <v>45966</v>
+      </c>
+      <c r="AF6" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="AG6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH6" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="AI6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ6" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>45458</v>
       </c>
@@ -1517,8 +2433,62 @@
       <c r="R7" s="12" t="s">
         <v>125</v>
       </c>
+      <c r="S7" s="13">
+        <v>45906</v>
+      </c>
+      <c r="T7" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="U7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="W7" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="X7" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y7" s="16">
+        <v>45936</v>
+      </c>
+      <c r="Z7" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="AC7" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD7" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AE7" s="16">
+        <v>45967</v>
+      </c>
+      <c r="AF7" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG7" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ7" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" ht="69" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>45459</v>
       </c>
@@ -1573,8 +2543,62 @@
       <c r="R8" s="12" t="s">
         <v>163</v>
       </c>
+      <c r="S8" s="13">
+        <v>45907</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="U8" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="V8" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y8" s="16">
+        <v>45937</v>
+      </c>
+      <c r="Z8" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD8" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE8" s="16">
+        <v>45968</v>
+      </c>
+      <c r="AF8" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI8" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="AJ8" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="9" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>45460</v>
       </c>
@@ -1629,8 +2653,62 @@
       <c r="R9" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S9" s="13">
+        <v>45908</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="W9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X9" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y9" s="16">
+        <v>45938</v>
+      </c>
+      <c r="Z9" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="AC9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE9" s="16">
+        <v>45969</v>
+      </c>
+      <c r="AF9" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG9" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="AH9" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ9" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:18" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>45461</v>
       </c>
@@ -1685,8 +2763,62 @@
       <c r="R10" s="12" t="s">
         <v>34</v>
       </c>
+      <c r="S10" s="13">
+        <v>45909</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="U10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X10" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y10" s="16">
+        <v>45939</v>
+      </c>
+      <c r="Z10" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE10" s="16">
+        <v>45970</v>
+      </c>
+      <c r="AF10" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="AG10" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="AH10" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="AI10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ10" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="11" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>45462</v>
       </c>
@@ -1741,8 +2873,62 @@
       <c r="R11" s="12" t="s">
         <v>125</v>
       </c>
+      <c r="S11" s="13">
+        <v>45910</v>
+      </c>
+      <c r="T11" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="U11" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="V11" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="W11" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="X11" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y11" s="16">
+        <v>45940</v>
+      </c>
+      <c r="Z11" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="AA11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="AC11" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="AD11" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE11" s="16">
+        <v>45971</v>
+      </c>
+      <c r="AF11" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="AG11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH11" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="AI11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ11" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="12" spans="1:18" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>45463</v>
       </c>
@@ -1797,8 +2983,62 @@
       <c r="R12" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S12" s="13">
+        <v>45911</v>
+      </c>
+      <c r="T12" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="U12" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="V12" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="W12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" s="16">
+        <v>45941</v>
+      </c>
+      <c r="Z12" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="AA12" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB12" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD12" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE12" s="16">
+        <v>45972</v>
+      </c>
+      <c r="AF12" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ12" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="13" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>45464</v>
       </c>
@@ -1849,8 +3089,62 @@
       </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="12"/>
+      <c r="S13" s="13">
+        <v>45912</v>
+      </c>
+      <c r="T13" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="U13" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="V13" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="W13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X13" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y13" s="16">
+        <v>45942</v>
+      </c>
+      <c r="Z13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AB13" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD13" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="16">
+        <v>45973</v>
+      </c>
+      <c r="AF13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH13" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="AI13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ13" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="14" spans="1:18" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>45465</v>
       </c>
@@ -1905,8 +3199,62 @@
       <c r="R14" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S14" s="13">
+        <v>45913</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="U14" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="V14" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="W14" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="X14" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y14" s="16">
+        <v>45943</v>
+      </c>
+      <c r="Z14" s="17" t="s">
+        <v>307</v>
+      </c>
+      <c r="AA14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC14" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD14" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE14" s="16">
+        <v>45974</v>
+      </c>
+      <c r="AF14" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="AG14" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="AH14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI14" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="AJ14" s="18" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="15" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>45466</v>
       </c>
@@ -1961,8 +3309,62 @@
       <c r="R15" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S15" s="13">
+        <v>45914</v>
+      </c>
+      <c r="T15" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="U15" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="V15" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="W15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y15" s="16">
+        <v>45944</v>
+      </c>
+      <c r="Z15" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="AC15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE15" s="16">
+        <v>45975</v>
+      </c>
+      <c r="AF15" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="AG15" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AH15" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AI15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>45467</v>
       </c>
@@ -2017,8 +3419,62 @@
       <c r="R16" s="12" t="s">
         <v>163</v>
       </c>
+      <c r="S16" s="13">
+        <v>45915</v>
+      </c>
+      <c r="T16" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V16" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="W16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X16" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>45945</v>
+      </c>
+      <c r="Z16" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="AA16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AC16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE16" s="16">
+        <v>45976</v>
+      </c>
+      <c r="AF16" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="AG16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI16" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ16" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="17" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>45468</v>
       </c>
@@ -2073,8 +3529,62 @@
       <c r="R17" s="12" t="s">
         <v>163</v>
       </c>
+      <c r="S17" s="13">
+        <v>45916</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="V17" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="W17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X17" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>45946</v>
+      </c>
+      <c r="Z17" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="AC17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE17" s="16">
+        <v>45977</v>
+      </c>
+      <c r="AF17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="AH17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI17" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="AJ17" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="18" spans="1:18" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>45469</v>
       </c>
@@ -2129,8 +3639,62 @@
       <c r="R18" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S18" s="13">
+        <v>45917</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="U18" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="V18" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="W18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>45947</v>
+      </c>
+      <c r="Z18" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="AA18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="AC18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE18" s="16">
+        <v>45978</v>
+      </c>
+      <c r="AF18" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="AG18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH18" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="AI18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ18" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="19" spans="1:18" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>45470</v>
       </c>
@@ -2185,8 +3749,62 @@
       <c r="R19" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S19" s="13">
+        <v>45918</v>
+      </c>
+      <c r="T19" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V19" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="W19" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X19" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y19" s="16">
+        <v>45948</v>
+      </c>
+      <c r="Z19" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="AC19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE19" s="16">
+        <v>45979</v>
+      </c>
+      <c r="AF19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG19" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="AH19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI19" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="AJ19" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="20" spans="1:18" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>45471</v>
       </c>
@@ -2241,8 +3859,62 @@
       <c r="R20" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S20" s="13">
+        <v>45919</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="U20" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="W20" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X20" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y20" s="16">
+        <v>45949</v>
+      </c>
+      <c r="Z20" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="AA20" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="AB20" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="AC20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE20" s="16">
+        <v>45980</v>
+      </c>
+      <c r="AF20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG20" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="AH20" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ20" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="21" spans="1:18" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>45472</v>
       </c>
@@ -2297,8 +3969,62 @@
       <c r="R21" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S21" s="13">
+        <v>45920</v>
+      </c>
+      <c r="T21" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="U21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V21" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="W21" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y21" s="16">
+        <v>45950</v>
+      </c>
+      <c r="Z21" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="AA21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC21" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD21" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE21" s="16">
+        <v>45981</v>
+      </c>
+      <c r="AF21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG21" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="AH21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AJ21" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="22" spans="1:18" ht="69" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" ht="69" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>45473</v>
       </c>
@@ -2353,8 +4079,62 @@
       <c r="R22" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S22" s="13">
+        <v>45921</v>
+      </c>
+      <c r="T22" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V22" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="W22" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X22" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y22" s="16">
+        <v>45951</v>
+      </c>
+      <c r="Z22" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="AA22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB22" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="AC22" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="AD22" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE22" s="16">
+        <v>45982</v>
+      </c>
+      <c r="AF22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG22" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="AH22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI22" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="AJ22" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="23" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -2397,8 +4177,62 @@
       <c r="R23" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S23" s="13">
+        <v>45922</v>
+      </c>
+      <c r="T23" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="U23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V23" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y23" s="16">
+        <v>45952</v>
+      </c>
+      <c r="Z23" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="AA23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB23" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD23" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AE23" s="16">
+        <v>45983</v>
+      </c>
+      <c r="AF23" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="AG23" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="AH23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI23" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="AJ23" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="24" spans="1:18" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -2441,8 +4275,62 @@
       <c r="R24" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S24" s="13">
+        <v>45923</v>
+      </c>
+      <c r="T24" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="U24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V24" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="W24" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X24" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y24" s="16">
+        <v>45953</v>
+      </c>
+      <c r="Z24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD24" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE24" s="16">
+        <v>45984</v>
+      </c>
+      <c r="AF24" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG24" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="AH24" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="AI24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ24" s="18" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="25" spans="1:18" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2485,8 +4373,62 @@
       <c r="R25" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S25" s="13">
+        <v>45924</v>
+      </c>
+      <c r="T25" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="U25" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V25" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="W25" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X25" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y25" s="16">
+        <v>45954</v>
+      </c>
+      <c r="Z25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD25" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE25" s="16">
+        <v>45985</v>
+      </c>
+      <c r="AF25" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="AG25" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="AH25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ25" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="26" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -2529,8 +4471,62 @@
       <c r="R26" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S26" s="13">
+        <v>45925</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="U26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V26" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="W26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="X26" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y26" s="16">
+        <v>45955</v>
+      </c>
+      <c r="Z26" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA26" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB26" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="AC26" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD26" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE26" s="16">
+        <v>45986</v>
+      </c>
+      <c r="AF26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG26" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="AH26" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="AI26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ26" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="27" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" ht="69" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -2571,8 +4567,62 @@
       <c r="R27" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S27" s="13">
+        <v>45926</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="U27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V27" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="W27" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X27" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y27" s="16">
+        <v>45956</v>
+      </c>
+      <c r="Z27" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="AC27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD27" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE27" s="16">
+        <v>45987</v>
+      </c>
+      <c r="AF27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="AH27" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="AI27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ27" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="28" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -2615,8 +4665,62 @@
       <c r="R28" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S28" s="13">
+        <v>45927</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="U28" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="V28" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="W28" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X28" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y28" s="16">
+        <v>45957</v>
+      </c>
+      <c r="Z28" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB28" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="AC28" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD28" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE28" s="16">
+        <v>45988</v>
+      </c>
+      <c r="AF28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG28" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="AH28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI28" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ28" s="18" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="29" spans="1:18" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -2659,8 +4763,62 @@
       <c r="R29" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S29" s="13">
+        <v>45928</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="V29" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="W29" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X29" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y29" s="16">
+        <v>45958</v>
+      </c>
+      <c r="Z29" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="AA29" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB29" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD29" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE29" s="16">
+        <v>45989</v>
+      </c>
+      <c r="AF29" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="AG29" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="AH29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI29" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ29" s="18" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="30" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2703,8 +4861,62 @@
       <c r="R30" s="12" t="s">
         <v>121</v>
       </c>
+      <c r="S30" s="13">
+        <v>45929</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="U30" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V30" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="W30" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y30" s="16">
+        <v>45959</v>
+      </c>
+      <c r="Z30" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="AA30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD30" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE30" s="16">
+        <v>45990</v>
+      </c>
+      <c r="AF30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG30" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="AH30" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI30" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="AJ30" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="31" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -2747,8 +4959,63 @@
       <c r="R31" s="12" t="s">
         <v>15</v>
       </c>
+      <c r="S31" s="13">
+        <v>45930</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="U31" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="V31" s="14">
+        <f>-W32</f>
+        <v>0</v>
+      </c>
+      <c r="W31" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="X31" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y31" s="16">
+        <v>45960</v>
+      </c>
+      <c r="Z31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD31" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE31" s="16">
+        <v>45991</v>
+      </c>
+      <c r="AF31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH31" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AI31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ31" s="18" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -2792,6 +5059,627 @@
         <v>116</v>
       </c>
     </row>
+    <row r="35" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="J35" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="R35" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>385</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="36" spans="8:35" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="N36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="O36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="S36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="T36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="U36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="V36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="W36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="X36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="Y36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="Z36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="AA36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="AB36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="AC36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AD36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="AE36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="AF36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="AG36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="AH36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="AI36" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="37" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H37" s="20"/>
+      <c r="I37" s="20">
+        <v>1</v>
+      </c>
+      <c r="J37" s="20">
+        <v>2</v>
+      </c>
+      <c r="K37" s="20">
+        <v>3</v>
+      </c>
+      <c r="L37" s="21">
+        <v>4</v>
+      </c>
+      <c r="M37" s="21">
+        <v>5</v>
+      </c>
+      <c r="N37" s="20">
+        <v>6</v>
+      </c>
+      <c r="O37" s="20"/>
+      <c r="P37" s="20"/>
+      <c r="Q37" s="20"/>
+      <c r="R37" s="20"/>
+      <c r="S37" s="20">
+        <v>1</v>
+      </c>
+      <c r="T37" s="20">
+        <v>2</v>
+      </c>
+      <c r="U37" s="20">
+        <v>3</v>
+      </c>
+      <c r="V37" s="20">
+        <v>1</v>
+      </c>
+      <c r="W37" s="20">
+        <v>2</v>
+      </c>
+      <c r="X37" s="20">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="21">
+        <v>4</v>
+      </c>
+      <c r="Z37" s="21">
+        <v>5</v>
+      </c>
+      <c r="AA37" s="20">
+        <v>6</v>
+      </c>
+      <c r="AB37" s="20">
+        <v>7</v>
+      </c>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="20"/>
+      <c r="AE37" s="21">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="20">
+        <v>2</v>
+      </c>
+      <c r="AG37" s="21">
+        <v>3</v>
+      </c>
+      <c r="AH37" s="20">
+        <v>4</v>
+      </c>
+      <c r="AI37" s="20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H38" s="20">
+        <v>7</v>
+      </c>
+      <c r="I38" s="20">
+        <v>8</v>
+      </c>
+      <c r="J38" s="20">
+        <v>9</v>
+      </c>
+      <c r="K38" s="20">
+        <v>10</v>
+      </c>
+      <c r="L38" s="20">
+        <v>11</v>
+      </c>
+      <c r="M38" s="20">
+        <v>12</v>
+      </c>
+      <c r="N38" s="21">
+        <v>13</v>
+      </c>
+      <c r="O38" s="20">
+        <v>4</v>
+      </c>
+      <c r="P38" s="20">
+        <v>5</v>
+      </c>
+      <c r="Q38" s="20">
+        <v>6</v>
+      </c>
+      <c r="R38" s="20">
+        <v>7</v>
+      </c>
+      <c r="S38" s="21">
+        <v>8</v>
+      </c>
+      <c r="T38" s="20">
+        <v>9</v>
+      </c>
+      <c r="U38" s="20">
+        <v>10</v>
+      </c>
+      <c r="V38" s="20">
+        <v>8</v>
+      </c>
+      <c r="W38" s="22">
+        <v>9</v>
+      </c>
+      <c r="X38" s="20">
+        <v>10</v>
+      </c>
+      <c r="Y38" s="22">
+        <v>11</v>
+      </c>
+      <c r="Z38" s="22">
+        <v>12</v>
+      </c>
+      <c r="AA38" s="22">
+        <v>13</v>
+      </c>
+      <c r="AB38" s="21">
+        <v>14</v>
+      </c>
+      <c r="AC38" s="20">
+        <v>6</v>
+      </c>
+      <c r="AD38" s="20">
+        <v>7</v>
+      </c>
+      <c r="AE38" s="20">
+        <v>8</v>
+      </c>
+      <c r="AF38" s="20">
+        <v>9</v>
+      </c>
+      <c r="AG38" s="20">
+        <v>10</v>
+      </c>
+      <c r="AH38" s="20">
+        <v>11</v>
+      </c>
+      <c r="AI38" s="20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H39" s="20">
+        <v>14</v>
+      </c>
+      <c r="I39" s="22">
+        <v>15</v>
+      </c>
+      <c r="J39" s="20">
+        <v>16</v>
+      </c>
+      <c r="K39" s="20">
+        <v>17</v>
+      </c>
+      <c r="L39" s="20">
+        <v>18</v>
+      </c>
+      <c r="M39" s="21">
+        <v>19</v>
+      </c>
+      <c r="N39" s="20">
+        <v>20</v>
+      </c>
+      <c r="O39" s="20">
+        <v>11</v>
+      </c>
+      <c r="P39" s="21">
+        <v>12</v>
+      </c>
+      <c r="Q39" s="20">
+        <v>13</v>
+      </c>
+      <c r="R39" s="20">
+        <v>14</v>
+      </c>
+      <c r="S39" s="21">
+        <v>15</v>
+      </c>
+      <c r="T39" s="20">
+        <v>16</v>
+      </c>
+      <c r="U39" s="21">
+        <v>17</v>
+      </c>
+      <c r="V39" s="20">
+        <v>15</v>
+      </c>
+      <c r="W39" s="20">
+        <v>16</v>
+      </c>
+      <c r="X39" s="20">
+        <v>17</v>
+      </c>
+      <c r="Y39" s="20">
+        <v>18</v>
+      </c>
+      <c r="Z39" s="20">
+        <v>19</v>
+      </c>
+      <c r="AA39" s="20">
+        <v>20</v>
+      </c>
+      <c r="AB39" s="20">
+        <v>21</v>
+      </c>
+      <c r="AC39" s="20">
+        <v>13</v>
+      </c>
+      <c r="AD39" s="20">
+        <v>14</v>
+      </c>
+      <c r="AE39" s="20">
+        <v>15</v>
+      </c>
+      <c r="AF39" s="20">
+        <v>16</v>
+      </c>
+      <c r="AG39" s="22">
+        <v>17</v>
+      </c>
+      <c r="AH39" s="21">
+        <v>18</v>
+      </c>
+      <c r="AI39" s="22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H40" s="21">
+        <v>21</v>
+      </c>
+      <c r="I40" s="20">
+        <v>22</v>
+      </c>
+      <c r="J40" s="20">
+        <v>23</v>
+      </c>
+      <c r="K40" s="20">
+        <v>24</v>
+      </c>
+      <c r="L40" s="20">
+        <v>25</v>
+      </c>
+      <c r="M40" s="20">
+        <v>26</v>
+      </c>
+      <c r="N40" s="22">
+        <v>27</v>
+      </c>
+      <c r="O40" s="20">
+        <v>18</v>
+      </c>
+      <c r="P40" s="20">
+        <v>19</v>
+      </c>
+      <c r="Q40" s="22">
+        <v>20</v>
+      </c>
+      <c r="R40" s="21">
+        <v>21</v>
+      </c>
+      <c r="S40" s="22">
+        <v>22</v>
+      </c>
+      <c r="T40" s="20">
+        <v>23</v>
+      </c>
+      <c r="U40" s="20">
+        <v>24</v>
+      </c>
+      <c r="V40" s="20">
+        <v>22</v>
+      </c>
+      <c r="W40" s="20">
+        <v>23</v>
+      </c>
+      <c r="X40" s="20">
+        <v>24</v>
+      </c>
+      <c r="Y40" s="22">
+        <v>25</v>
+      </c>
+      <c r="Z40" s="20">
+        <v>26</v>
+      </c>
+      <c r="AA40" s="22">
+        <v>27</v>
+      </c>
+      <c r="AB40" s="22">
+        <v>28</v>
+      </c>
+      <c r="AC40" s="20">
+        <v>20</v>
+      </c>
+      <c r="AD40" s="21">
+        <v>21</v>
+      </c>
+      <c r="AE40" s="20">
+        <v>22</v>
+      </c>
+      <c r="AF40" s="20">
+        <v>23</v>
+      </c>
+      <c r="AG40" s="20">
+        <v>24</v>
+      </c>
+      <c r="AH40" s="20">
+        <v>25</v>
+      </c>
+      <c r="AI40" s="20">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H41" s="22">
+        <v>28</v>
+      </c>
+      <c r="I41" s="20">
+        <v>29</v>
+      </c>
+      <c r="J41" s="22">
+        <v>30</v>
+      </c>
+      <c r="K41" s="20">
+        <v>31</v>
+      </c>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="O41" s="20">
+        <v>25</v>
+      </c>
+      <c r="P41" s="21">
+        <v>26</v>
+      </c>
+      <c r="Q41" s="20">
+        <v>27</v>
+      </c>
+      <c r="R41" s="21">
+        <v>28</v>
+      </c>
+      <c r="S41" s="21">
+        <v>29</v>
+      </c>
+      <c r="T41" s="22">
+        <v>30</v>
+      </c>
+      <c r="U41" s="20">
+        <v>31</v>
+      </c>
+      <c r="V41" s="22">
+        <v>29</v>
+      </c>
+      <c r="W41" s="21">
+        <v>30</v>
+      </c>
+      <c r="AC41" s="20">
+        <v>27</v>
+      </c>
+      <c r="AD41" s="20">
+        <v>28</v>
+      </c>
+      <c r="AE41" s="20">
+        <v>29</v>
+      </c>
+      <c r="AF41" s="20">
+        <v>30</v>
+      </c>
+      <c r="AG41" s="20">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="J45" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="46" spans="8:35" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="H46" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="M46" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="N46" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="20">
+        <v>1</v>
+      </c>
+      <c r="N47" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="8:35" x14ac:dyDescent="0.3">
+      <c r="H48" s="21">
+        <v>3</v>
+      </c>
+      <c r="I48" s="20">
+        <v>4</v>
+      </c>
+      <c r="J48" s="20">
+        <v>5</v>
+      </c>
+      <c r="K48" s="20">
+        <v>6</v>
+      </c>
+      <c r="L48" s="20">
+        <v>7</v>
+      </c>
+      <c r="M48" s="20">
+        <v>8</v>
+      </c>
+      <c r="N48" s="22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="H49" s="21">
+        <v>10</v>
+      </c>
+      <c r="I49" s="21">
+        <v>11</v>
+      </c>
+      <c r="J49" s="20">
+        <v>12</v>
+      </c>
+      <c r="K49" s="20">
+        <v>13</v>
+      </c>
+      <c r="L49" s="21">
+        <v>14</v>
+      </c>
+      <c r="M49" s="23">
+        <v>15</v>
+      </c>
+      <c r="N49" s="20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="H50" s="21">
+        <v>17</v>
+      </c>
+      <c r="I50" s="20">
+        <v>18</v>
+      </c>
+      <c r="J50" s="20">
+        <v>19</v>
+      </c>
+      <c r="K50" s="20">
+        <v>20</v>
+      </c>
+      <c r="L50" s="20">
+        <v>21</v>
+      </c>
+      <c r="M50" s="20">
+        <v>22</v>
+      </c>
+      <c r="N50" s="20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="8:14" x14ac:dyDescent="0.3">
+      <c r="H51" s="21">
+        <v>24</v>
+      </c>
+      <c r="I51" s="20">
+        <v>25</v>
+      </c>
+      <c r="J51" s="20">
+        <v>26</v>
+      </c>
+      <c r="K51" s="20">
+        <v>27</v>
+      </c>
+      <c r="L51" s="22">
+        <v>28</v>
+      </c>
+      <c r="M51" s="20">
+        <v>29</v>
+      </c>
+      <c r="N51" s="20">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Meses pasados.xlsx
+++ b/Meses pasados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emili\OneDrive\Escritorio\Visual\bitacora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03F0FDE-6EFD-4118-8475-7DB98D152E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22AE54C7-B6CF-4D50-A9AC-B4E895C9AA82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="636">
   <si>
     <t>DIA</t>
   </si>
@@ -1197,6 +1197,753 @@
   </si>
   <si>
     <t>OCTUBRE</t>
+  </si>
+  <si>
+    <t>Comimos el recalentado de ayer</t>
+  </si>
+  <si>
+    <t>Churro con salsa que hizo Josef</t>
+  </si>
+  <si>
+    <t>Unas tortillas con jamon y luego en el carnaval una granita y luego una orden de pupusas</t>
+  </si>
+  <si>
+    <t>Mamá hizo unas tortillas fritas con carnita del recalentado y una ensaladita</t>
+  </si>
+  <si>
+    <t>Hice unas baleadas</t>
+  </si>
+  <si>
+    <t>Semitas con café</t>
+  </si>
+  <si>
+    <t>Compraron una pizza de papizza</t>
+  </si>
+  <si>
+    <t>Fui a tomar un cafe con mis amigas</t>
+  </si>
+  <si>
+    <t>Comi lo ultimo que quedaba de pantorreja y un pedazo de pizza adicional</t>
+  </si>
+  <si>
+    <t>Fuimos a comer una parrillada por el cumpleaños de papá</t>
+  </si>
+  <si>
+    <t>Me hice unas baleadas</t>
+  </si>
+  <si>
+    <t>Mamá hizo un pollo con arroz y frjoles, ademas una carnita que quedó de ayer</t>
+  </si>
+  <si>
+    <t>Churrp</t>
+  </si>
+  <si>
+    <t>Frijoles con salsa</t>
+  </si>
+  <si>
+    <t>Hice una carne en el asador y mamá hizo un arroz y frijoles po rel cumple de papá</t>
+  </si>
+  <si>
+    <t>Pastel 3 leches</t>
+  </si>
+  <si>
+    <t>Tambien otro pedazo de pastel y algunas uvas</t>
+  </si>
+  <si>
+    <t>Mamá hizo webo con frijoles aguacate y tortillas</t>
+  </si>
+  <si>
+    <t>Una platada de atun con churro</t>
+  </si>
+  <si>
+    <t>Papá milagrosamente hizo webo xon frijoles y unos chorizos</t>
+  </si>
+  <si>
+    <t>Cereal y tambien un atun con churro</t>
+  </si>
+  <si>
+    <t>Hice un arroz y Alex fue a comprar pollo frito</t>
+  </si>
+  <si>
+    <t>Hice un webo y tambien tortilla con jamon</t>
+  </si>
+  <si>
+    <t>Mamá hizo tacos normales con hotdog y arroz</t>
+  </si>
+  <si>
+    <t>Un poco de pure de papa que dejó mamá, arroz y frijoles</t>
+  </si>
+  <si>
+    <t>Lo que quedó de pasta</t>
+  </si>
+  <si>
+    <t>Pollo frito con una ensalada y arroz namas</t>
+  </si>
+  <si>
+    <t>Ya que mis papas salieron hice unas chuletas con arroz para nosotros, ademas tome un poco de zidra</t>
+  </si>
+  <si>
+    <t>Me hice un atun que me dieron y con churro</t>
+  </si>
+  <si>
+    <t>Mamá hizo unos tacos de hotgod</t>
+  </si>
+  <si>
+    <t>Me hizo unas tortillas con quesillo</t>
+  </si>
+  <si>
+    <t>Hambriento por alguna razon</t>
+  </si>
+  <si>
+    <t>Ya que mis padres se fueron de nuevo hice carne molida con arroz y tortilla ademas de un batido tipo nestum</t>
+  </si>
+  <si>
+    <t>Pan con cafe ademas de un poco de comida de la tarde</t>
+  </si>
+  <si>
+    <t>Con hambre aunque comi bastante digo yo</t>
+  </si>
+  <si>
+    <t>Mamá hizo webo en torta (hace tiempo no comia), frijoles y arroz</t>
+  </si>
+  <si>
+    <t>Pan con el batido tipo nestum</t>
+  </si>
+  <si>
+    <t>Con hambre</t>
+  </si>
+  <si>
+    <t>Comimos en burguer king por mi cita en el dentista</t>
+  </si>
+  <si>
+    <t>Un hotdog de los que venden en circle K</t>
+  </si>
+  <si>
+    <t>Mamá hizo una sopa de res</t>
+  </si>
+  <si>
+    <t>Me comi una carnita cona arroz que habian dejado</t>
+  </si>
+  <si>
+    <t>Como ahora hacen comida aca entonces Irma hizo una pasta</t>
+  </si>
+  <si>
+    <t>Tambien lo mismmo de la tarde</t>
+  </si>
+  <si>
+    <t>Un poco de pollo que asaber desde hace cuanto lo compraron</t>
+  </si>
+  <si>
+    <t>Unos panecillos que compraron</t>
+  </si>
+  <si>
+    <t>Pnqueques qu</t>
+  </si>
+  <si>
+    <t>Pollo con arroz y frijoles</t>
+  </si>
+  <si>
+    <t>Comi unos fideos de arroz ademas de arroz chino junto con verduras y luego un pastel en el cumple</t>
+  </si>
+  <si>
+    <t>Super lleno, a reventar</t>
+  </si>
+  <si>
+    <t>Un poco de fideos que traje del cumple junto con unas papas que habia hecho y arroz</t>
+  </si>
+  <si>
+    <t>Solo pan con cafe</t>
+  </si>
+  <si>
+    <t>Un pedazo de pollo</t>
+  </si>
+  <si>
+    <t>Ya que llegó mi mamá entonces compraron unos tacos</t>
+  </si>
+  <si>
+    <t>Webo con frijoles, platano y pan tostadp con chimichurri y salsa ahhhh</t>
+  </si>
+  <si>
+    <t>Un pedazo de pollo y un churro que dejó mi sobrino</t>
+  </si>
+  <si>
+    <t>Issa me invitó una burrita por Zambrano</t>
+  </si>
+  <si>
+    <t>Salimos a comer a un lugar de venta de comidas y pedo unas tajadas enormes</t>
+  </si>
+  <si>
+    <t>Fuimos al mismo lugar del almuerzo a por una sopa de res (deliciosa)</t>
+  </si>
+  <si>
+    <t>Issa me hizó unos webos con frijoles y chorizitos con tortillas en su casa</t>
+  </si>
+  <si>
+    <t>Semita y chocolate caliente</t>
+  </si>
+  <si>
+    <t>Hice unas burritas caseras bien completas (webo,frijoles,quesillo)</t>
+  </si>
+  <si>
+    <t>Fui a la casa sde abuela y me dio una arne molida con verduras, arroz y trotillas</t>
+  </si>
+  <si>
+    <t>El chocolate que me diste</t>
+  </si>
+  <si>
+    <t>Me hice un atun y lo comi con churro</t>
+  </si>
+  <si>
+    <t>Sardians con arroz y un pedacito de pollo</t>
+  </si>
+  <si>
+    <t>Hice una carne en al freidora para la noche</t>
+  </si>
+  <si>
+    <t>De las carnes que hice ayer, frijoles fritos y unas papas ensalsadas de pollo campesino</t>
+  </si>
+  <si>
+    <t>Tortillas con quesillo y webo</t>
+  </si>
+  <si>
+    <t>El arroz chino con tu familia</t>
+  </si>
+  <si>
+    <t>Unos pedazos de pollo agridulce con arroz que dejaron (Delicia pura)</t>
+  </si>
+  <si>
+    <t>Quesadilla</t>
+  </si>
+  <si>
+    <t>Bastante lleno</t>
+  </si>
+  <si>
+    <t>Una carnita asada y chorizos que hicieron en cane ademas de ensalda</t>
+  </si>
+  <si>
+    <t>Una burrita que me compró Irma</t>
+  </si>
+  <si>
+    <t>2 Quesadillas</t>
+  </si>
+  <si>
+    <t>Un pedazo de pollo con ensalada de papas de pollo campesino y me hice un mini sandwich de webo y queso</t>
+  </si>
+  <si>
+    <t>Nacatamal</t>
+  </si>
+  <si>
+    <t>Raramente me hice un repollo con un poco de tajaditas y pedacitos de carne aunque le añadi mas tortillas fritas y salsa</t>
+  </si>
+  <si>
+    <t>Una platada de repollo y me hice una carnita molida con salsa que sobró de ayer</t>
+  </si>
+  <si>
+    <t>Sopa instantanea y webo cocido</t>
+  </si>
+  <si>
+    <t>bastante lleno</t>
+  </si>
+  <si>
+    <t>Me hice un poco de repollo con frijoles licuados y algo de pollo sobrante</t>
+  </si>
+  <si>
+    <t>Un nestum casero</t>
+  </si>
+  <si>
+    <t>Evidentemente mas pasta</t>
+  </si>
+  <si>
+    <t>Aun sobraba pasta asi que me la terminé</t>
+  </si>
+  <si>
+    <t>No me acuerdo</t>
+  </si>
+  <si>
+    <t>No se</t>
+  </si>
+  <si>
+    <t>La carneada en mi cumple</t>
+  </si>
+  <si>
+    <t>La hamburguesa que Josef nos compró</t>
+  </si>
+  <si>
+    <t>Solamente me compré 2 sopas instantaneas y me hice unos webos hervidos</t>
+  </si>
+  <si>
+    <t>Unos frijoles con mantequilla</t>
+  </si>
+  <si>
+    <t>Dulce me dió una galleta</t>
+  </si>
+  <si>
+    <t>Me hice un arroz con frijoles y sardinas</t>
+  </si>
+  <si>
+    <t>Josef me compró baleadas</t>
+  </si>
+  <si>
+    <t>Me hice un poco de carne molida y combine con arroz</t>
+  </si>
+  <si>
+    <t>Un poco de pollo</t>
+  </si>
+  <si>
+    <t>Un postre raro que habia</t>
+  </si>
+  <si>
+    <t>Hice pollo y comi con un arroz sobrante</t>
+  </si>
+  <si>
+    <t>Me hice un webo con platano y luego calente tortillas con quesillo</t>
+  </si>
+  <si>
+    <t>El postre que me diste y ademas un poco de frijoles con churro y pollo</t>
+  </si>
+  <si>
+    <t>Fuimos a comer unas chuletas a mar y tierra</t>
+  </si>
+  <si>
+    <t>Hice un atun que habia y con churro</t>
+  </si>
+  <si>
+    <t>Mamá hizo un webo en torta y frijoles licuados</t>
+  </si>
+  <si>
+    <t>Pizza que compró papá</t>
+  </si>
+  <si>
+    <t>Dulce</t>
+  </si>
+  <si>
+    <t>Un pedacito de pizza que sobró y algo mas que no recuerdo</t>
+  </si>
+  <si>
+    <t>Unas tortillas con quesillo y webo con chimichurri</t>
+  </si>
+  <si>
+    <t>Una galleta que me dió Dulce</t>
+  </si>
+  <si>
+    <t>Hice arroz y un pollo con salsa que hizo Josef pero yo hice el pollo antes jajaj</t>
+  </si>
+  <si>
+    <t>Un pedazo de pollo que trajo papá y hice platano con algo de arroz que sobró</t>
+  </si>
+  <si>
+    <t>Tambien comi pasta</t>
+  </si>
+  <si>
+    <t>Chocolate</t>
+  </si>
+  <si>
+    <t>Hice otro pollo y comi con frijoles creo</t>
+  </si>
+  <si>
+    <t>Josef me dió una comida que estaba ahi, era una carnita con un poco de tajadas</t>
+  </si>
+  <si>
+    <t>Un pollo sobrante</t>
+  </si>
+  <si>
+    <t>Frijoles con un poco de churro</t>
+  </si>
+  <si>
+    <t>Me hice ynas baleadas</t>
+  </si>
+  <si>
+    <t>Irma compro un shapsui de arroz creo</t>
+  </si>
+  <si>
+    <t>Paleta</t>
+  </si>
+  <si>
+    <t>Fideos de ayer</t>
+  </si>
+  <si>
+    <t>Tambien fideos</t>
+  </si>
+  <si>
+    <t>Me hice una carnita molida con arroz y me comi unas 5 tortillas con un platote de todo</t>
+  </si>
+  <si>
+    <t>Nada (estaba demasiado lleno)</t>
+  </si>
+  <si>
+    <t>Muylleno</t>
+  </si>
+  <si>
+    <t>Comi fideos de arroz que auuuuun queda</t>
+  </si>
+  <si>
+    <t>Ps lo mismo</t>
+  </si>
+  <si>
+    <t>Fui donde mamita y me dió un "desayuno" de webo con fijoles y cafe, y luego una sopa de almuerzo</t>
+  </si>
+  <si>
+    <t>Fideos</t>
+  </si>
+  <si>
+    <t>Lo que me diste en la u y luego un webo</t>
+  </si>
+  <si>
+    <t>Comi unas papas con un sadwich creo, que dejaron, ademas me hice mas papas hervidas y frijoles</t>
+  </si>
+  <si>
+    <t>2 sopas instantaneas con huevo cocido</t>
+  </si>
+  <si>
+    <t>Frijoles con queso y platano</t>
+  </si>
+  <si>
+    <t>Pan con jugo</t>
+  </si>
+  <si>
+    <t>Un poco de pasta de ayer</t>
+  </si>
+  <si>
+    <t>Lo que sobró de pasta</t>
+  </si>
+  <si>
+    <t>Josef me trajo algo de arroz chino (regular)</t>
+  </si>
+  <si>
+    <t>Ps lo que fuimos a comer con Issa</t>
+  </si>
+  <si>
+    <t>Josef me trajo un mil hojas</t>
+  </si>
+  <si>
+    <t>Comi algode frijoles liquados que habia con churro, platano webo ademas del juguito</t>
+  </si>
+  <si>
+    <t>Josef trajó unos "chilaquiles" aunque ni traian salsa asi que hice una</t>
+  </si>
+  <si>
+    <t>Irma me trajo una burrita</t>
+  </si>
+  <si>
+    <t>No se la verdad</t>
+  </si>
+  <si>
+    <t>Me hice unos espaguettys</t>
+  </si>
+  <si>
+    <t>Mas pasta evidentemente</t>
+  </si>
+  <si>
+    <t>Pasta del dia anterior</t>
+  </si>
+  <si>
+    <t>Una carnita que me trajo Josef ayer</t>
+  </si>
+  <si>
+    <t>Comimos en el mall de Comayagua y yo comi fideos de arroz</t>
+  </si>
+  <si>
+    <t>Una sobrina de mi papá llegó a hacer pupusas y quedaron delis</t>
+  </si>
+  <si>
+    <t>Pupusas que sobraron de ayer y frijoles</t>
+  </si>
+  <si>
+    <t>Tortillas con quesillo y webo, ademas de una salsa</t>
+  </si>
+  <si>
+    <t>Me hice unas tortillas fritas y junto con un salsa que ya habia hecho comi rico</t>
+  </si>
+  <si>
+    <t>Frijoles y aun arroz que hizo Irma</t>
+  </si>
+  <si>
+    <t>Hice unos sandwiches caseros</t>
+  </si>
+  <si>
+    <t>Nestum casero</t>
+  </si>
+  <si>
+    <t>LLeno</t>
+  </si>
+  <si>
+    <t>Me hice unas baleadas? aunque eran como burritas con todo pero hechas en tortillas de baleada</t>
+  </si>
+  <si>
+    <t>Josef me dió unas baleadas y no podia rechazarlas aunque estuviera lleno</t>
+  </si>
+  <si>
+    <t>Pan blanco</t>
+  </si>
+  <si>
+    <t>Una chuletita con arroz y frijoles</t>
+  </si>
+  <si>
+    <t>Me compré una baleada en la U</t>
+  </si>
+  <si>
+    <t>Algo de frijoles con arroz</t>
+  </si>
+  <si>
+    <t>Fuimos a comer una parrillada por el dia del padre a Comayagua</t>
+  </si>
+  <si>
+    <t>2 sopas instantaneas</t>
+  </si>
+  <si>
+    <t>Mamá hizo una mini ensaldad de repollo con tomate y se junto con pollo</t>
+  </si>
+  <si>
+    <t>Josef compró comida asi que comi algo de carne con frijoles y demas</t>
+  </si>
+  <si>
+    <t>Me hice unas burritas caseras que me llenaron a full</t>
+  </si>
+  <si>
+    <t>Nadamas unos pan moldes con salsa</t>
+  </si>
+  <si>
+    <t>Mamá me trajo un poco de pollo y con frijoles</t>
+  </si>
+  <si>
+    <t>Me hice un poco repollo con churro y salsa</t>
+  </si>
+  <si>
+    <t>De ayer sobró algo de repollo y me hice un pure de papas ademas de frijoles liquados de super jaja</t>
+  </si>
+  <si>
+    <t>Hice arroz con sardina</t>
+  </si>
+  <si>
+    <t>Hice una carne molida con webo y tambien arroz como con 4 tortillas</t>
+  </si>
+  <si>
+    <t>Unas pupusas que josef compró</t>
+  </si>
+  <si>
+    <t>Me compre unas baleadas en la U</t>
+  </si>
+  <si>
+    <t>Issa me dió un poco de sandia y una semita gigante</t>
+  </si>
+  <si>
+    <t>Frijoles con arroz</t>
+  </si>
+  <si>
+    <t>La carneada que yo hice y ademas frijoles, etc.</t>
+  </si>
+  <si>
+    <t>Unas tortillas con jamon y queso</t>
+  </si>
+  <si>
+    <t>Ya que me fui temparno solo comi un nacatamal</t>
+  </si>
+  <si>
+    <t>LLegando a casa me hice un arroz y comi la carne nmolida que quedaba</t>
+  </si>
+  <si>
+    <t>Un pan de minimo</t>
+  </si>
+  <si>
+    <t>Un poco de pollo y ensaldad de papas de pollo campesino</t>
+  </si>
+  <si>
+    <t>Fui a donde mamita asi que me dió una sopita de pollo</t>
+  </si>
+  <si>
+    <t>Irma hizo una pasta rara de guacamole con pollo y tipo sandwich, pero, estaba deliciosa</t>
+  </si>
+  <si>
+    <t>Mas pasta obvioo</t>
+  </si>
+  <si>
+    <t>Frijoles liquados y los junte con churro</t>
+  </si>
+  <si>
+    <t>Irma hizo panqueques</t>
+  </si>
+  <si>
+    <t>Algo vacio</t>
+  </si>
+  <si>
+    <t>Unos tacos mexicanos que uffffff</t>
+  </si>
+  <si>
+    <t>Josef me dió en la tarde unas papas de popeyes asi que comi mientras estudiaba</t>
+  </si>
+  <si>
+    <t>Junto con el resto de las papas y un mini sandwich comi</t>
+  </si>
+  <si>
+    <t>Josef me dió una medio comidita que compró</t>
+  </si>
+  <si>
+    <t>Frijoles con churro</t>
+  </si>
+  <si>
+    <t>Vacioo</t>
+  </si>
+  <si>
+    <t>Me comi un pollo que dejaron y algo mas que no recuerdo</t>
+  </si>
+  <si>
+    <t>Hice el batido Nestum pero ademas con papaya</t>
+  </si>
+  <si>
+    <t>Solamente me hice unas sopas instantaneas</t>
+  </si>
+  <si>
+    <t>Burritas caseras</t>
+  </si>
+  <si>
+    <t>Me compré unas baleadas en la U</t>
+  </si>
+  <si>
+    <t>Llegando a casa me compre un pollo con arroz</t>
+  </si>
+  <si>
+    <t>Arroz con frijoles</t>
+  </si>
+  <si>
+    <t>Un pan de pan</t>
+  </si>
+  <si>
+    <t>Mamá hizo una carne molida con webo y una mini ensalada</t>
+  </si>
+  <si>
+    <t>Baleadas hechas por mi</t>
+  </si>
+  <si>
+    <t>Bastate lleno</t>
+  </si>
+  <si>
+    <t>Mamá hizo sopa de frijoles (hace tiempo no tomaba)</t>
+  </si>
+  <si>
+    <t>Fuimos a Comayagua entonces comi chuleta pero de la que llena</t>
+  </si>
+  <si>
+    <t>Tortillas con jamon y un poco de frijoles</t>
+  </si>
+  <si>
+    <t>Mamá hizo sopa de pescado (muy rica primera vez)</t>
+  </si>
+  <si>
+    <t>Agarré arroz y un poco de sopa que quedó</t>
+  </si>
+  <si>
+    <t>Pan con café</t>
+  </si>
+  <si>
+    <t>Fuimos a comer a la Paz y pedi una costilla de cerdo</t>
+  </si>
+  <si>
+    <t>Una minuta en el parque</t>
+  </si>
+  <si>
+    <t>Me hice unas tortillas con quesillo y webo y un pan</t>
+  </si>
+  <si>
+    <t>Hicieron pollo chuco casero (aqui ya me sentia un poco mal)</t>
+  </si>
+  <si>
+    <t>Con lyzzi comimos una minuta y tambien me dió una paleta</t>
+  </si>
+  <si>
+    <t>Comi un poco de sopa de pescado aunque la vomite toda</t>
+  </si>
+  <si>
+    <t>Enfermo</t>
+  </si>
+  <si>
+    <t>Un pan con té, luego una manzana</t>
+  </si>
+  <si>
+    <t>Mamá me hizo un sopa magi y luego un puré con arroz</t>
+  </si>
+  <si>
+    <t>Vacio y enfermo</t>
+  </si>
+  <si>
+    <t>Josef me hizo una sopa de pollo con papa</t>
+  </si>
+  <si>
+    <t>Para la cena lo mismo</t>
+  </si>
+  <si>
+    <t>Me comi algo de pollo con un webo y pan molde</t>
+  </si>
+  <si>
+    <t>Josef me hizo un webo estrellado, algo de frijoles liquados</t>
+  </si>
+  <si>
+    <t>Deficiente pero sarisfecho</t>
+  </si>
+  <si>
+    <t>Antes de salir un fresco de avena</t>
+  </si>
+  <si>
+    <t>Agarre un poco de pollo ensalsado que ahi estaba ademas de arroz ya que llegue tarde</t>
+  </si>
+  <si>
+    <t>nada</t>
+  </si>
+  <si>
+    <t>No se, normal</t>
+  </si>
+  <si>
+    <t>Mas pasta obviooo</t>
+  </si>
+  <si>
+    <t>Hice unas chuletas y comi papa hervida con queso (super rico)</t>
+  </si>
+  <si>
+    <t>Un poco de nestum casero</t>
+  </si>
+  <si>
+    <t>Compré alguans cosas e hice unos sandwiches</t>
+  </si>
+  <si>
+    <t>Hervi un poco de lechuga, hice platano y agarre frijoles liquados de hace mucho tiempo ademas de una chuleta de ayer</t>
+  </si>
+  <si>
+    <t>Solo papas hervidas</t>
+  </si>
+  <si>
+    <t>Josef me hizo un mini desayuno de webo y frijoles con platano</t>
+  </si>
+  <si>
+    <t>Me compró unos tacos mexicanos super ricos</t>
+  </si>
+  <si>
+    <t>Ya que m eiba a cane solo me hice unos frijoles con papas hervidas y queso con platano</t>
+  </si>
+  <si>
+    <t>Frijoles y un ensaladaque estaba por ahi ademas de café con quesadilla y pan</t>
+  </si>
+  <si>
+    <t>Papá hizo frijoles y se compró unas sardinas con arroz</t>
+  </si>
+  <si>
+    <t>Trotillas con jamon y jugo</t>
+  </si>
+  <si>
+    <t>Pasta con churro</t>
+  </si>
+  <si>
+    <t>Bien bien</t>
+  </si>
+  <si>
+    <t>ENERO</t>
+  </si>
+  <si>
+    <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>MARZO</t>
+  </si>
+  <si>
+    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -1246,7 +1993,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1306,6 +2053,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF268256"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0408D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1350,7 +2109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1421,11 +2180,20 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1708,7 +2476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ51"/>
+  <dimension ref="A1:BR41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="46.88671875" customWidth="1"/>
@@ -1718,7 +2486,7 @@
     <col min="16" max="16" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1827,8 +2595,80 @@
       <c r="AJ1" s="10" t="s">
         <v>5</v>
       </c>
+      <c r="AK1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AX1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AZ1" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="BA1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="BB1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="BD1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE1" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF1" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="BG1" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="BH1" s="26" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>45453</v>
       </c>
@@ -1937,8 +2777,60 @@
       <c r="AJ2" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK2" s="13">
+        <v>45658</v>
+      </c>
+      <c r="AL2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM2" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="AN2" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="AO2" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="AQ2" s="16">
+        <v>45689</v>
+      </c>
+      <c r="AR2" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="AS2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT2" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="AU2" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="AV2" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="AW2" s="16">
+        <v>45717</v>
+      </c>
+      <c r="AX2" s="17"/>
+      <c r="AY2" s="17"/>
+      <c r="AZ2" s="17"/>
+      <c r="BA2" s="17"/>
+      <c r="BB2" s="18"/>
+      <c r="BC2" s="16">
+        <v>45748</v>
+      </c>
+      <c r="BD2" s="17"/>
+      <c r="BE2" s="17"/>
+      <c r="BF2" s="17"/>
+      <c r="BG2" s="17"/>
+      <c r="BH2" s="18"/>
     </row>
-    <row r="3" spans="1:36" ht="69" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>45454</v>
       </c>
@@ -2047,8 +2939,60 @@
       <c r="AJ3" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK3" s="13">
+        <v>45659</v>
+      </c>
+      <c r="AL3" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="AM3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN3" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="AO3" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AQ3" s="16">
+        <v>45690</v>
+      </c>
+      <c r="AR3" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="AS3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT3" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="AU3" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="AV3" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW3" s="16">
+        <v>45718</v>
+      </c>
+      <c r="AX3" s="17"/>
+      <c r="AY3" s="17"/>
+      <c r="AZ3" s="17"/>
+      <c r="BA3" s="17"/>
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="16">
+        <v>45749</v>
+      </c>
+      <c r="BD3" s="17"/>
+      <c r="BE3" s="17"/>
+      <c r="BF3" s="17"/>
+      <c r="BG3" s="17"/>
+      <c r="BH3" s="18"/>
     </row>
-    <row r="4" spans="1:36" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>45455</v>
       </c>
@@ -2157,8 +3101,70 @@
       <c r="AJ4" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK4" s="13">
+        <v>45660</v>
+      </c>
+      <c r="AL4" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="AM4" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="AN4" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="AO4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP4" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ4" s="16">
+        <v>45691</v>
+      </c>
+      <c r="AR4" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="AS4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT4" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="AU4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV4" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW4" s="16">
+        <v>45719</v>
+      </c>
+      <c r="AX4" s="17"/>
+      <c r="AY4" s="17"/>
+      <c r="AZ4" s="17"/>
+      <c r="BA4" s="17"/>
+      <c r="BB4" s="18"/>
+      <c r="BC4" s="16">
+        <v>45750</v>
+      </c>
+      <c r="BD4" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF4" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="BG4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH4" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>45456</v>
       </c>
@@ -2267,8 +3273,70 @@
       <c r="AJ5" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK5" s="13">
+        <v>45661</v>
+      </c>
+      <c r="AL5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM5" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="AN5" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="AO5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ5" s="16">
+        <v>45692</v>
+      </c>
+      <c r="AR5" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="AS5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV5" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="AW5" s="16">
+        <v>45720</v>
+      </c>
+      <c r="AX5" s="17"/>
+      <c r="AY5" s="17"/>
+      <c r="AZ5" s="17"/>
+      <c r="BA5" s="17"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="16">
+        <v>45751</v>
+      </c>
+      <c r="BD5" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="BE5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG5" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="BH5" s="18" t="s">
+        <v>575</v>
+      </c>
     </row>
-    <row r="6" spans="1:36" ht="69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>45457</v>
       </c>
@@ -2377,8 +3445,58 @@
       <c r="AJ6" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK6" s="13">
+        <v>45662</v>
+      </c>
+      <c r="AL6" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="AM6" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="AN6" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="AO6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP6" s="15"/>
+      <c r="AQ6" s="16">
+        <v>45693</v>
+      </c>
+      <c r="AR6" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="AS6" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT6" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="AU6" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="AV6" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="AW6" s="16">
+        <v>45721</v>
+      </c>
+      <c r="AX6" s="17"/>
+      <c r="AY6" s="17"/>
+      <c r="AZ6" s="17"/>
+      <c r="BA6" s="17"/>
+      <c r="BB6" s="18"/>
+      <c r="BC6" s="16">
+        <v>45752</v>
+      </c>
+      <c r="BD6" s="17"/>
+      <c r="BE6" s="17"/>
+      <c r="BF6" s="17"/>
+      <c r="BG6" s="17"/>
+      <c r="BH6" s="18"/>
     </row>
-    <row r="7" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>45458</v>
       </c>
@@ -2487,8 +3605,80 @@
       <c r="AJ7" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK7" s="13">
+        <v>45663</v>
+      </c>
+      <c r="AL7" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="AM7" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="AN7" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="AO7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP7" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ7" s="16">
+        <v>45694</v>
+      </c>
+      <c r="AR7" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="AS7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU7" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="AV7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW7" s="16">
+        <v>45722</v>
+      </c>
+      <c r="AX7" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY7" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="AZ7" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="BA7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB7" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC7" s="16">
+        <v>45753</v>
+      </c>
+      <c r="BD7" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="BE7" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="BF7" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="BG7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH7" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" ht="69" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" ht="69" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>45459</v>
       </c>
@@ -2597,8 +3787,80 @@
       <c r="AJ8" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK8" s="13">
+        <v>45664</v>
+      </c>
+      <c r="AL8" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="AM8" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO8" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="AP8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ8" s="16">
+        <v>45695</v>
+      </c>
+      <c r="AR8" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="AS8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT8" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="AU8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV8" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW8" s="16">
+        <v>45723</v>
+      </c>
+      <c r="AX8" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="AY8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ8" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="BA8" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="BB8" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC8" s="16">
+        <v>45754</v>
+      </c>
+      <c r="BD8" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="BE8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF8" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="BG8" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH8" s="18" t="s">
+        <v>581</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>45460</v>
       </c>
@@ -2707,8 +3969,80 @@
       <c r="AJ9" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK9" s="13">
+        <v>45665</v>
+      </c>
+      <c r="AL9" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="AM9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN9" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="AO9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP9" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AQ9" s="16">
+        <v>45696</v>
+      </c>
+      <c r="AR9" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="AS9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT9" s="17" t="s">
+        <v>473</v>
+      </c>
+      <c r="AU9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV9" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="AW9" s="16">
+        <v>45724</v>
+      </c>
+      <c r="AX9" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="AY9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA9" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="BB9" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC9" s="16">
+        <v>45755</v>
+      </c>
+      <c r="BD9" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF9" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG9" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH9" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>45461</v>
       </c>
@@ -2817,8 +4151,80 @@
       <c r="AJ10" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK10" s="15">
+        <v>9</v>
+      </c>
+      <c r="AL10" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="AM10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN10" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="AO10" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AP10" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ10" s="16">
+        <v>45697</v>
+      </c>
+      <c r="AR10" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="AS10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT10" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="AU10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW10" s="16">
+        <v>45725</v>
+      </c>
+      <c r="AX10" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="AY10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ10" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB10" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC10" s="16">
+        <v>45756</v>
+      </c>
+      <c r="BD10" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="BE10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF10" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="BG10" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH10" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>45462</v>
       </c>
@@ -2927,8 +4333,80 @@
       <c r="AJ11" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK11" s="13">
+        <v>45667</v>
+      </c>
+      <c r="AL11" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="AM11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN11" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO11" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="AP11" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ11" s="16">
+        <v>45698</v>
+      </c>
+      <c r="AR11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS11" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="AT11" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="AU11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV11" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW11" s="16">
+        <v>45726</v>
+      </c>
+      <c r="AX11" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AY11" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="AZ11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA11" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="BB11" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC11" s="16">
+        <v>45757</v>
+      </c>
+      <c r="BD11" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="BE11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF11" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="BG11" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH11" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>45463</v>
       </c>
@@ -3037,8 +4515,80 @@
       <c r="AJ12" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK12" s="13">
+        <v>45668</v>
+      </c>
+      <c r="AL12" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="AM12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AO12" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="AP12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="16">
+        <v>45699</v>
+      </c>
+      <c r="AR12" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="AS12" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="AT12" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="AU12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV12" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW12" s="16">
+        <v>45727</v>
+      </c>
+      <c r="AX12" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="AY12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB12" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC12" s="16">
+        <v>45758</v>
+      </c>
+      <c r="BD12" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="BE12" s="17" t="s">
+        <v>587</v>
+      </c>
+      <c r="BF12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG12" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="BH12" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" ht="69" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>45464</v>
       </c>
@@ -3143,8 +4693,80 @@
       <c r="AJ13" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK13" s="13">
+        <v>45669</v>
+      </c>
+      <c r="AL13" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="AM13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN13" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AO13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="AP13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ13" s="16">
+        <v>45700</v>
+      </c>
+      <c r="AR13" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="AS13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT13" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="AU13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV13" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW13" s="16">
+        <v>45728</v>
+      </c>
+      <c r="AX13" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="AY13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ13" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="BA13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB13" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="BC13" s="16">
+        <v>45759</v>
+      </c>
+      <c r="BD13" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="BE13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG13" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="BH13" s="18" t="s">
+        <v>135</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>45465</v>
       </c>
@@ -3253,8 +4875,74 @@
       <c r="AJ14" s="18" t="s">
         <v>96</v>
       </c>
+      <c r="AK14" s="13">
+        <v>45670</v>
+      </c>
+      <c r="AL14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AM14" s="14"/>
+      <c r="AN14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO14" s="14"/>
+      <c r="AP14" s="15"/>
+      <c r="AQ14" s="16">
+        <v>45701</v>
+      </c>
+      <c r="AR14" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="AS14" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="AT14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU14" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="AV14" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW14" s="16">
+        <v>45729</v>
+      </c>
+      <c r="AX14" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="AY14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ14" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB14" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC14" s="16">
+        <v>45760</v>
+      </c>
+      <c r="BD14" s="17" t="s">
+        <v>590</v>
+      </c>
+      <c r="BE14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF14" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="BG14" s="17" t="s">
+        <v>591</v>
+      </c>
+      <c r="BH14" s="18" t="s">
+        <v>592</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>45466</v>
       </c>
@@ -3363,8 +5051,80 @@
       <c r="AJ15" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK15" s="13">
+        <v>45671</v>
+      </c>
+      <c r="AL15" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="AM15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO15" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="AP15" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ15" s="16">
+        <v>45702</v>
+      </c>
+      <c r="AR15" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="AS15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT15" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="AU15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV15" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW15" s="16">
+        <v>45730</v>
+      </c>
+      <c r="AX15" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="AY15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ15" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB15" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC15" s="16">
+        <v>45761</v>
+      </c>
+      <c r="BD15" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="BE15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG15" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="BH15" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>45467</v>
       </c>
@@ -3473,8 +5233,80 @@
       <c r="AJ16" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK16" s="13">
+        <v>45672</v>
+      </c>
+      <c r="AL16" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="AM16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN16" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="AO16" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AP16" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="AQ16" s="16">
+        <v>45703</v>
+      </c>
+      <c r="AR16" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="AS16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT16" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="AU16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV16" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW16" s="16">
+        <v>45731</v>
+      </c>
+      <c r="AX16" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="AY16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ16" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="BA16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB16" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC16" s="16">
+        <v>45762</v>
+      </c>
+      <c r="BD16" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="BE16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF16" s="17" t="s">
+        <v>595</v>
+      </c>
+      <c r="BG16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH16" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="17" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:60" ht="138" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>45468</v>
       </c>
@@ -3583,8 +5415,80 @@
       <c r="AJ17" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK17" s="13">
+        <v>45673</v>
+      </c>
+      <c r="AL17" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="AM17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN17" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="AO17" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP17" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="AQ17" s="16">
+        <v>45704</v>
+      </c>
+      <c r="AR17" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="AS17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT17" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="AU17" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="AV17" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW17" s="16">
+        <v>45732</v>
+      </c>
+      <c r="AX17" s="17" t="s">
+        <v>536</v>
+      </c>
+      <c r="AY17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA17" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="BB17" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC17" s="16">
+        <v>45763</v>
+      </c>
+      <c r="BD17" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="BE17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF17" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="BG17" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="BH17" s="18" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="18" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>45469</v>
       </c>
@@ -3693,8 +5597,80 @@
       <c r="AJ18" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK18" s="13">
+        <v>45674</v>
+      </c>
+      <c r="AL18" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="AM18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN18" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="AO18" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP18" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="AQ18" s="16">
+        <v>45705</v>
+      </c>
+      <c r="AR18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS18" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="AT18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU18" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="AV18" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW18" s="16">
+        <v>45733</v>
+      </c>
+      <c r="AX18" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="AY18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA18" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="BB18" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC18" s="16">
+        <v>45764</v>
+      </c>
+      <c r="BD18" s="17" t="s">
+        <v>599</v>
+      </c>
+      <c r="BE18" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="BF18" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="BG18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH18" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="19" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>45470</v>
       </c>
@@ -3803,8 +5779,80 @@
       <c r="AJ19" s="18" t="s">
         <v>116</v>
       </c>
+      <c r="AK19" s="13">
+        <v>45675</v>
+      </c>
+      <c r="AL19" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="AM19" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN19" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="AO19" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP19" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ19" s="16">
+        <v>45706</v>
+      </c>
+      <c r="AR19" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="AS19" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="AT19" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="AU19" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="AV19" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW19" s="16">
+        <v>45734</v>
+      </c>
+      <c r="AX19" s="17" t="s">
+        <v>540</v>
+      </c>
+      <c r="AY19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA19" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="BB19" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="BC19" s="16">
+        <v>45765</v>
+      </c>
+      <c r="BD19" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="BE19" s="17" t="s">
+        <v>603</v>
+      </c>
+      <c r="BF19" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="BG19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH19" s="18" t="s">
+        <v>605</v>
+      </c>
     </row>
-    <row r="20" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:60" ht="138" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>45471</v>
       </c>
@@ -3913,8 +5961,80 @@
       <c r="AJ20" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK20" s="13">
+        <v>45676</v>
+      </c>
+      <c r="AL20" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="AM20" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN20" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO20" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="AP20" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ20" s="16">
+        <v>45707</v>
+      </c>
+      <c r="AR20" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="AS20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT20" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="AU20" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="AV20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW20" s="16">
+        <v>45735</v>
+      </c>
+      <c r="AX20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY20" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="AZ20" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="BA20" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="BB20" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="BC20" s="16">
+        <v>45766</v>
+      </c>
+      <c r="BD20" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="BE20" s="17" t="s">
+        <v>607</v>
+      </c>
+      <c r="BF20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH20" s="18" t="s">
+        <v>608</v>
+      </c>
     </row>
-    <row r="21" spans="1:36" ht="138" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:60" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>45472</v>
       </c>
@@ -4023,8 +6143,80 @@
       <c r="AJ21" s="18" t="s">
         <v>116</v>
       </c>
+      <c r="AK21" s="13">
+        <v>45677</v>
+      </c>
+      <c r="AL21" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="AM21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN21" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="AO21" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP21" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AQ21" s="16">
+        <v>45708</v>
+      </c>
+      <c r="AR21" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="AS21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU21" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="AV21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW21" s="16">
+        <v>45736</v>
+      </c>
+      <c r="AX21" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="AY21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA21" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="BB21" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC21" s="16">
+        <v>45767</v>
+      </c>
+      <c r="BD21" s="17" t="s">
+        <v>609</v>
+      </c>
+      <c r="BE21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF21" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="BG21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH21" s="18" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="22" spans="1:36" ht="69" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:60" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>45473</v>
       </c>
@@ -4133,8 +6325,80 @@
       <c r="AJ22" s="18" t="s">
         <v>116</v>
       </c>
+      <c r="AK22" s="13">
+        <v>45678</v>
+      </c>
+      <c r="AL22" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="AM22" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="AN22" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="AO22" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="AP22" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ22" s="16">
+        <v>45709</v>
+      </c>
+      <c r="AR22" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="AS22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU22" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="AV22" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AW22" s="16">
+        <v>45737</v>
+      </c>
+      <c r="AX22" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="AY22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ22" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="BA22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB22" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC22" s="16">
+        <v>45768</v>
+      </c>
+      <c r="BD22" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="BE22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF22" s="17" t="s">
+        <v>612</v>
+      </c>
+      <c r="BG22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH22" s="18" t="s">
+        <v>613</v>
+      </c>
     </row>
-    <row r="23" spans="1:36" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:60" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -4231,8 +6495,80 @@
       <c r="AJ23" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK23" s="13">
+        <v>45679</v>
+      </c>
+      <c r="AL23" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="AM23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN23" s="14" t="s">
+        <v>435</v>
+      </c>
+      <c r="AO23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP23" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="AQ23" s="16">
+        <v>45710</v>
+      </c>
+      <c r="AR23" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="AS23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT23" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="AU23" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="AV23" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW23" s="16">
+        <v>45738</v>
+      </c>
+      <c r="AX23" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="AY23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA23" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB23" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC23" s="16">
+        <v>45769</v>
+      </c>
+      <c r="BD23" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="BE23" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="BF23" s="17" t="s">
+        <v>616</v>
+      </c>
+      <c r="BG23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH23" s="18" t="s">
+        <v>617</v>
+      </c>
     </row>
-    <row r="24" spans="1:36" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -4329,8 +6665,80 @@
       <c r="AJ24" s="18" t="s">
         <v>96</v>
       </c>
+      <c r="AK24" s="13">
+        <v>45680</v>
+      </c>
+      <c r="AL24" s="14" t="s">
+        <v>437</v>
+      </c>
+      <c r="AM24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN24" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="AO24" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="AP24" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ24" s="16">
+        <v>45711</v>
+      </c>
+      <c r="AR24" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="AS24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU24" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="AV24" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW24" s="16">
+        <v>45739</v>
+      </c>
+      <c r="AX24" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="AY24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ24" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="BA24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB24" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="BC24" s="16">
+        <v>45770</v>
+      </c>
+      <c r="BD24" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="BE24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF24" s="17" t="s">
+        <v>618</v>
+      </c>
+      <c r="BG24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH24" s="18" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="25" spans="1:36" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4427,8 +6835,76 @@
       <c r="AJ25" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK25" s="13">
+        <v>45681</v>
+      </c>
+      <c r="AL25" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="AM25" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="AN25" s="14" t="s">
+        <v>441</v>
+      </c>
+      <c r="AO25" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP25" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ25" s="16">
+        <v>45712</v>
+      </c>
+      <c r="AR25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS25" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="AT25" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="AU25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV25" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="AW25" s="16">
+        <v>45740</v>
+      </c>
+      <c r="AX25" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="AY25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ25" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="BA25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB25" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC25" s="16">
+        <v>45771</v>
+      </c>
+      <c r="BD25" s="17"/>
+      <c r="BE25" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="BF25" s="17"/>
+      <c r="BG25" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="BH25" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="26" spans="1:36" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:60" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -4525,8 +7001,80 @@
       <c r="AJ26" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK26" s="13">
+        <v>45682</v>
+      </c>
+      <c r="AL26" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="AM26" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="AN26" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="AO26" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP26" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="AQ26" s="16">
+        <v>45713</v>
+      </c>
+      <c r="AR26" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="AS26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU26" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="AV26" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW26" s="16">
+        <v>45741</v>
+      </c>
+      <c r="AX26" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="AY26" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA26" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="BB26" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC26" s="16">
+        <v>45772</v>
+      </c>
+      <c r="BD26" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="BE26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF26" s="17" t="s">
+        <v>622</v>
+      </c>
+      <c r="BG26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH26" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="27" spans="1:36" ht="69" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:60" ht="138" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -4621,8 +7169,80 @@
       <c r="AJ27" s="18" t="s">
         <v>121</v>
       </c>
+      <c r="AK27" s="13">
+        <v>45683</v>
+      </c>
+      <c r="AL27" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="AM27" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN27" s="14" t="s">
+        <v>446</v>
+      </c>
+      <c r="AO27" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP27" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AQ27" s="16">
+        <v>45714</v>
+      </c>
+      <c r="AR27" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="AS27" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT27" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="AU27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV27" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW27" s="16">
+        <v>45742</v>
+      </c>
+      <c r="AX27" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="AY27" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="AZ27" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="BA27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB27" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC27" s="16">
+        <v>45773</v>
+      </c>
+      <c r="BD27" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="BE27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF27" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="BG27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH27" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="28" spans="1:36" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:60" ht="138" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4719,8 +7339,80 @@
       <c r="AJ28" s="18" t="s">
         <v>10</v>
       </c>
+      <c r="AK28" s="13">
+        <v>45684</v>
+      </c>
+      <c r="AL28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM28" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="AN28" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO28" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP28" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="AQ28" s="16">
+        <v>45715</v>
+      </c>
+      <c r="AR28" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="AS28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU28" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="AV28" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW28" s="16">
+        <v>45743</v>
+      </c>
+      <c r="AX28" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="AY28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ28" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="BA28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB28" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC28" s="16">
+        <v>45774</v>
+      </c>
+      <c r="BD28" s="17" t="s">
+        <v>624</v>
+      </c>
+      <c r="BE28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF28" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="BG28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH28" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="29" spans="1:36" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:60" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -4817,8 +7509,80 @@
       <c r="AJ29" s="18" t="s">
         <v>163</v>
       </c>
+      <c r="AK29" s="13">
+        <v>45685</v>
+      </c>
+      <c r="AL29" s="14" t="s">
+        <v>448</v>
+      </c>
+      <c r="AM29" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN29" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO29" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP29" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AQ29" s="16">
+        <v>45716</v>
+      </c>
+      <c r="AR29" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="AS29" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="AT29" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="AU29" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="AV29" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW29" s="16">
+        <v>45744</v>
+      </c>
+      <c r="AX29" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="AY29" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="AZ29" s="17" t="s">
+        <v>563</v>
+      </c>
+      <c r="BA29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB29" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="BC29" s="16">
+        <v>45775</v>
+      </c>
+      <c r="BD29" s="17" t="s">
+        <v>626</v>
+      </c>
+      <c r="BE29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF29" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="BG29" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH29" s="18" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="30" spans="1:36" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -4915,8 +7679,62 @@
       <c r="AJ30" s="18" t="s">
         <v>15</v>
       </c>
+      <c r="AK30" s="13">
+        <v>45686</v>
+      </c>
+      <c r="AL30" s="14" t="s">
+        <v>449</v>
+      </c>
+      <c r="AM30" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="AN30" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="AO30" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="AP30" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW30" s="16">
+        <v>45745</v>
+      </c>
+      <c r="AX30" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="AY30" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AZ30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA30" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="BB30" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC30" s="16">
+        <v>45776</v>
+      </c>
+      <c r="BD30" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="BE30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF30" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="BG30" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH30" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="31" spans="1:36" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:60" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -5014,8 +7832,62 @@
       <c r="AJ31" s="18" t="s">
         <v>9</v>
       </c>
+      <c r="AK31" s="13">
+        <v>45687</v>
+      </c>
+      <c r="AL31" s="14" t="s">
+        <v>452</v>
+      </c>
+      <c r="AM31" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN31" s="14" t="s">
+        <v>453</v>
+      </c>
+      <c r="AO31" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP31" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW31" s="16">
+        <v>45746</v>
+      </c>
+      <c r="AX31" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="AY31" s="17" t="s">
+        <v>567</v>
+      </c>
+      <c r="AZ31" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="BA31" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="BB31" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC31" s="16">
+        <v>45777</v>
+      </c>
+      <c r="BD31" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF31" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="BG31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH31" s="18" t="s">
+        <v>631</v>
+      </c>
     </row>
-    <row r="32" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:60" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -5058,8 +7930,44 @@
       <c r="R32" s="12" t="s">
         <v>116</v>
       </c>
+      <c r="AK32" s="13">
+        <v>45688</v>
+      </c>
+      <c r="AL32" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="AM32" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN32" s="14" t="s">
+        <v>455</v>
+      </c>
+      <c r="AO32" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP32" s="15" t="s">
+        <v>302</v>
+      </c>
+      <c r="AW32" s="16">
+        <v>45747</v>
+      </c>
+      <c r="AX32" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="AY32" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ32" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA32" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="BB32" s="18" t="s">
+        <v>121</v>
+      </c>
     </row>
-    <row r="35" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="35" spans="8:70" x14ac:dyDescent="0.3">
       <c r="J35" s="24" t="s">
         <v>383</v>
       </c>
@@ -5072,8 +7980,23 @@
       <c r="AG35" t="s">
         <v>386</v>
       </c>
+      <c r="AL35" t="s">
+        <v>382</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>632</v>
+      </c>
+      <c r="BA35" s="28" t="s">
+        <v>633</v>
+      </c>
+      <c r="BH35" t="s">
+        <v>634</v>
+      </c>
+      <c r="BO35" t="s">
+        <v>635</v>
+      </c>
     </row>
-    <row r="36" spans="8:35" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="8:70" ht="26.4" x14ac:dyDescent="0.3">
       <c r="H36" s="19" t="s">
         <v>375</v>
       </c>
@@ -5158,8 +8081,113 @@
       <c r="AI36" s="19" t="s">
         <v>381</v>
       </c>
+      <c r="AJ36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="AL36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="AM36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="AN36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="AO36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="AP36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="AQ36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AR36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="AS36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="AT36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="AU36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="AV36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="AW36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="AX36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="AY36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="AZ36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="BA36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="BB36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="BC36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="BD36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="BE36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="BF36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="BG36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="BH36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="BI36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="BJ36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="BK36" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="BL36" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="BM36" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="BN36" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="BO36" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="BP36" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="BQ36" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="BR36" s="19" t="s">
+        <v>381</v>
+      </c>
     </row>
-    <row r="37" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="37" spans="8:70" x14ac:dyDescent="0.3">
       <c r="H37" s="20"/>
       <c r="I37" s="20">
         <v>1</v>
@@ -5230,8 +8258,69 @@
       <c r="AI37" s="20">
         <v>5</v>
       </c>
+      <c r="AJ37" s="20"/>
+      <c r="AK37" s="20"/>
+      <c r="AL37" s="20"/>
+      <c r="AM37" s="20"/>
+      <c r="AN37" s="20"/>
+      <c r="AO37" s="20">
+        <v>1</v>
+      </c>
+      <c r="AP37" s="20">
+        <v>2</v>
+      </c>
+      <c r="AQ37" s="20"/>
+      <c r="AR37" s="20"/>
+      <c r="AS37" s="20"/>
+      <c r="AT37" s="21">
+        <v>1</v>
+      </c>
+      <c r="AU37" s="21">
+        <v>2</v>
+      </c>
+      <c r="AV37" s="20">
+        <v>3</v>
+      </c>
+      <c r="AW37" s="21">
+        <v>4</v>
+      </c>
+      <c r="AX37" s="20"/>
+      <c r="AY37" s="20"/>
+      <c r="AZ37" s="20"/>
+      <c r="BA37" s="20"/>
+      <c r="BB37" s="20"/>
+      <c r="BC37" s="20"/>
+      <c r="BD37" s="20">
+        <v>1</v>
+      </c>
+      <c r="BE37" s="20"/>
+      <c r="BF37" s="20"/>
+      <c r="BG37" s="20"/>
+      <c r="BH37" s="20"/>
+      <c r="BI37" s="20"/>
+      <c r="BJ37" s="20"/>
+      <c r="BK37" s="20">
+        <v>1</v>
+      </c>
+      <c r="BL37" s="20"/>
+      <c r="BM37" s="20"/>
+      <c r="BN37" s="20">
+        <v>1</v>
+      </c>
+      <c r="BO37" s="21">
+        <v>2</v>
+      </c>
+      <c r="BP37" s="20">
+        <v>3</v>
+      </c>
+      <c r="BQ37" s="20">
+        <v>4</v>
+      </c>
+      <c r="BR37" s="20">
+        <v>5</v>
+      </c>
     </row>
-    <row r="38" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="38" spans="8:70" x14ac:dyDescent="0.3">
       <c r="H38" s="20">
         <v>7</v>
       </c>
@@ -5316,8 +8405,113 @@
       <c r="AI38" s="20">
         <v>12</v>
       </c>
+      <c r="AJ38" s="21">
+        <v>3</v>
+      </c>
+      <c r="AK38" s="20">
+        <v>4</v>
+      </c>
+      <c r="AL38" s="20">
+        <v>5</v>
+      </c>
+      <c r="AM38" s="20">
+        <v>6</v>
+      </c>
+      <c r="AN38" s="20">
+        <v>7</v>
+      </c>
+      <c r="AO38" s="20">
+        <v>8</v>
+      </c>
+      <c r="AP38" s="22">
+        <v>9</v>
+      </c>
+      <c r="AQ38" s="21">
+        <v>5</v>
+      </c>
+      <c r="AR38" s="20">
+        <v>6</v>
+      </c>
+      <c r="AS38" s="20">
+        <v>7</v>
+      </c>
+      <c r="AT38" s="20">
+        <v>8</v>
+      </c>
+      <c r="AU38" s="20">
+        <v>9</v>
+      </c>
+      <c r="AV38" s="21">
+        <v>10</v>
+      </c>
+      <c r="AW38" s="20">
+        <v>11</v>
+      </c>
+      <c r="AX38" s="20">
+        <v>2</v>
+      </c>
+      <c r="AY38" s="21">
+        <v>3</v>
+      </c>
+      <c r="AZ38" s="20">
+        <v>4</v>
+      </c>
+      <c r="BA38" s="20">
+        <v>5</v>
+      </c>
+      <c r="BB38" s="27">
+        <v>6</v>
+      </c>
+      <c r="BC38" s="20">
+        <v>7</v>
+      </c>
+      <c r="BD38" s="20">
+        <v>8</v>
+      </c>
+      <c r="BE38" s="20">
+        <v>2</v>
+      </c>
+      <c r="BF38" s="20">
+        <v>3</v>
+      </c>
+      <c r="BG38" s="20">
+        <v>4</v>
+      </c>
+      <c r="BH38" s="21">
+        <v>5</v>
+      </c>
+      <c r="BI38" s="20">
+        <v>6</v>
+      </c>
+      <c r="BJ38" s="27">
+        <v>7</v>
+      </c>
+      <c r="BK38" s="20">
+        <v>8</v>
+      </c>
+      <c r="BL38" s="20">
+        <v>6</v>
+      </c>
+      <c r="BM38" s="20">
+        <v>7</v>
+      </c>
+      <c r="BN38" s="20">
+        <v>8</v>
+      </c>
+      <c r="BO38" s="20">
+        <v>9</v>
+      </c>
+      <c r="BP38" s="20">
+        <v>10</v>
+      </c>
+      <c r="BQ38" s="20">
+        <v>11</v>
+      </c>
+      <c r="BR38" s="20">
+        <v>12</v>
+      </c>
     </row>
-    <row r="39" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="39" spans="8:70" x14ac:dyDescent="0.3">
       <c r="H39" s="20">
         <v>14</v>
       </c>
@@ -5402,8 +8596,113 @@
       <c r="AI39" s="22">
         <v>19</v>
       </c>
+      <c r="AJ39" s="21">
+        <v>10</v>
+      </c>
+      <c r="AK39" s="21">
+        <v>11</v>
+      </c>
+      <c r="AL39" s="20">
+        <v>12</v>
+      </c>
+      <c r="AM39" s="20">
+        <v>13</v>
+      </c>
+      <c r="AN39" s="21">
+        <v>14</v>
+      </c>
+      <c r="AO39" s="23">
+        <v>15</v>
+      </c>
+      <c r="AP39" s="20">
+        <v>16</v>
+      </c>
+      <c r="AQ39" s="20">
+        <v>12</v>
+      </c>
+      <c r="AR39" s="27">
+        <v>13</v>
+      </c>
+      <c r="AS39" s="20">
+        <v>14</v>
+      </c>
+      <c r="AT39" s="21">
+        <v>15</v>
+      </c>
+      <c r="AU39" s="20">
+        <v>16</v>
+      </c>
+      <c r="AV39" s="20">
+        <v>17</v>
+      </c>
+      <c r="AW39" s="20">
+        <v>18</v>
+      </c>
+      <c r="AX39" s="20">
+        <v>9</v>
+      </c>
+      <c r="AY39" s="20">
+        <v>10</v>
+      </c>
+      <c r="AZ39" s="21">
+        <v>11</v>
+      </c>
+      <c r="BA39" s="20">
+        <v>12</v>
+      </c>
+      <c r="BB39" s="20">
+        <v>13</v>
+      </c>
+      <c r="BC39" s="20">
+        <v>14</v>
+      </c>
+      <c r="BD39" s="21">
+        <v>15</v>
+      </c>
+      <c r="BE39" s="21">
+        <v>9</v>
+      </c>
+      <c r="BF39" s="20">
+        <v>10</v>
+      </c>
+      <c r="BG39" s="20">
+        <v>11</v>
+      </c>
+      <c r="BH39" s="20">
+        <v>12</v>
+      </c>
+      <c r="BI39" s="20">
+        <v>13</v>
+      </c>
+      <c r="BJ39" s="20">
+        <v>14</v>
+      </c>
+      <c r="BK39" s="20">
+        <v>15</v>
+      </c>
+      <c r="BL39" s="20">
+        <v>13</v>
+      </c>
+      <c r="BM39" s="20">
+        <v>14</v>
+      </c>
+      <c r="BN39" s="20">
+        <v>15</v>
+      </c>
+      <c r="BO39" s="20">
+        <v>16</v>
+      </c>
+      <c r="BP39" s="20">
+        <v>17</v>
+      </c>
+      <c r="BQ39" s="20">
+        <v>18</v>
+      </c>
+      <c r="BR39" s="20">
+        <v>19</v>
+      </c>
     </row>
-    <row r="40" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="40" spans="8:70" x14ac:dyDescent="0.3">
       <c r="H40" s="21">
         <v>21</v>
       </c>
@@ -5488,8 +8787,113 @@
       <c r="AI40" s="20">
         <v>26</v>
       </c>
+      <c r="AJ40" s="21">
+        <v>17</v>
+      </c>
+      <c r="AK40" s="20">
+        <v>18</v>
+      </c>
+      <c r="AL40" s="20">
+        <v>19</v>
+      </c>
+      <c r="AM40" s="20">
+        <v>20</v>
+      </c>
+      <c r="AN40" s="20">
+        <v>21</v>
+      </c>
+      <c r="AO40" s="20">
+        <v>22</v>
+      </c>
+      <c r="AP40" s="20">
+        <v>23</v>
+      </c>
+      <c r="AQ40" s="20">
+        <v>19</v>
+      </c>
+      <c r="AR40" s="22">
+        <v>20</v>
+      </c>
+      <c r="AS40" s="20">
+        <v>21</v>
+      </c>
+      <c r="AT40" s="20">
+        <v>22</v>
+      </c>
+      <c r="AU40" s="21">
+        <v>23</v>
+      </c>
+      <c r="AV40" s="20">
+        <v>24</v>
+      </c>
+      <c r="AW40" s="20">
+        <v>25</v>
+      </c>
+      <c r="AX40" s="21">
+        <v>16</v>
+      </c>
+      <c r="AY40" s="20">
+        <v>17</v>
+      </c>
+      <c r="AZ40" s="21">
+        <v>18</v>
+      </c>
+      <c r="BA40" s="20">
+        <v>19</v>
+      </c>
+      <c r="BB40" s="20">
+        <v>20</v>
+      </c>
+      <c r="BC40" s="22">
+        <v>21</v>
+      </c>
+      <c r="BD40" s="20">
+        <v>22</v>
+      </c>
+      <c r="BE40" s="20">
+        <v>16</v>
+      </c>
+      <c r="BF40" s="20">
+        <v>17</v>
+      </c>
+      <c r="BG40" s="21">
+        <v>18</v>
+      </c>
+      <c r="BH40" s="22">
+        <v>19</v>
+      </c>
+      <c r="BI40" s="20">
+        <v>20</v>
+      </c>
+      <c r="BJ40" s="20">
+        <v>21</v>
+      </c>
+      <c r="BK40" s="20">
+        <v>22</v>
+      </c>
+      <c r="BL40" s="22">
+        <v>20</v>
+      </c>
+      <c r="BM40" s="20">
+        <v>21</v>
+      </c>
+      <c r="BN40" s="21">
+        <v>22</v>
+      </c>
+      <c r="BO40" s="20">
+        <v>23</v>
+      </c>
+      <c r="BP40" s="20">
+        <v>24</v>
+      </c>
+      <c r="BQ40" s="27">
+        <v>25</v>
+      </c>
+      <c r="BR40" s="20">
+        <v>26</v>
+      </c>
     </row>
-    <row r="41" spans="8:35" x14ac:dyDescent="0.3">
+    <row r="41" spans="8:70" x14ac:dyDescent="0.3">
       <c r="H41" s="22">
         <v>28</v>
       </c>
@@ -5546,139 +8950,98 @@
       <c r="AG41" s="20">
         <v>31</v>
       </c>
-    </row>
-    <row r="45" spans="8:35" x14ac:dyDescent="0.3">
-      <c r="J45" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="46" spans="8:35" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="H46" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="K46" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="L46" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="M46" s="19" t="s">
-        <v>380</v>
-      </c>
-      <c r="N46" s="19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="47" spans="8:35" x14ac:dyDescent="0.3">
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20">
-        <v>1</v>
-      </c>
-      <c r="N47" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="8:35" x14ac:dyDescent="0.3">
-      <c r="H48" s="21">
-        <v>3</v>
-      </c>
-      <c r="I48" s="20">
-        <v>4</v>
-      </c>
-      <c r="J48" s="20">
-        <v>5</v>
-      </c>
-      <c r="K48" s="20">
-        <v>6</v>
-      </c>
-      <c r="L48" s="20">
-        <v>7</v>
-      </c>
-      <c r="M48" s="20">
-        <v>8</v>
-      </c>
-      <c r="N48" s="22">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.3">
-      <c r="H49" s="21">
-        <v>10</v>
-      </c>
-      <c r="I49" s="21">
-        <v>11</v>
-      </c>
-      <c r="J49" s="20">
-        <v>12</v>
-      </c>
-      <c r="K49" s="20">
-        <v>13</v>
-      </c>
-      <c r="L49" s="21">
-        <v>14</v>
-      </c>
-      <c r="M49" s="23">
-        <v>15</v>
-      </c>
-      <c r="N49" s="20">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.3">
-      <c r="H50" s="21">
-        <v>17</v>
-      </c>
-      <c r="I50" s="20">
-        <v>18</v>
-      </c>
-      <c r="J50" s="20">
-        <v>19</v>
-      </c>
-      <c r="K50" s="20">
-        <v>20</v>
-      </c>
-      <c r="L50" s="20">
-        <v>21</v>
-      </c>
-      <c r="M50" s="20">
-        <v>22</v>
-      </c>
-      <c r="N50" s="20">
+      <c r="AJ41" s="21">
+        <v>24</v>
+      </c>
+      <c r="AK41" s="20">
+        <v>25</v>
+      </c>
+      <c r="AL41" s="20">
+        <v>26</v>
+      </c>
+      <c r="AM41" s="20">
+        <v>27</v>
+      </c>
+      <c r="AN41" s="22">
+        <v>28</v>
+      </c>
+      <c r="AO41" s="20">
+        <v>29</v>
+      </c>
+      <c r="AP41" s="20">
+        <v>30</v>
+      </c>
+      <c r="AQ41" s="20">
+        <v>26</v>
+      </c>
+      <c r="AR41" s="20">
+        <v>27</v>
+      </c>
+      <c r="AS41" s="27">
+        <v>28</v>
+      </c>
+      <c r="AT41" s="27">
+        <v>29</v>
+      </c>
+      <c r="AU41" s="20">
+        <v>30</v>
+      </c>
+      <c r="AV41" s="20">
+        <v>31</v>
+      </c>
+      <c r="AX41" s="20">
         <v>23</v>
       </c>
-    </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.3">
-      <c r="H51" s="21">
+      <c r="AY41" s="20">
         <v>24</v>
       </c>
-      <c r="I51" s="20">
+      <c r="AZ41" s="20">
         <v>25</v>
       </c>
-      <c r="J51" s="20">
+      <c r="BA41" s="21">
         <v>26</v>
       </c>
-      <c r="K51" s="20">
+      <c r="BB41" s="20">
         <v>27</v>
       </c>
-      <c r="L51" s="22">
+      <c r="BC41" s="21">
         <v>28</v>
       </c>
-      <c r="M51" s="20">
+      <c r="BE41" s="20">
+        <v>23</v>
+      </c>
+      <c r="BF41" s="20">
+        <v>24</v>
+      </c>
+      <c r="BG41" s="20">
+        <v>25</v>
+      </c>
+      <c r="BH41" s="20">
+        <v>26</v>
+      </c>
+      <c r="BI41" s="20">
+        <v>27</v>
+      </c>
+      <c r="BJ41" s="20">
+        <v>28</v>
+      </c>
+      <c r="BK41" s="21">
         <v>29</v>
       </c>
-      <c r="N51" s="20">
+      <c r="BL41" s="20">
+        <v>27</v>
+      </c>
+      <c r="BM41" s="20">
+        <v>28</v>
+      </c>
+      <c r="BN41" s="20">
+        <v>29</v>
+      </c>
+      <c r="BO41" s="21">
         <v>30</v>
       </c>
+      <c r="BP41" s="20"/>
+      <c r="BQ41" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
